--- a/data/raw/inbound/In_Transit_PO data.xlsx
+++ b/data/raw/inbound/In_Transit_PO data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inbound\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D673637-A660-43E7-998C-B33D57C8944C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -24517,522 +24517,520 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B12">
-    <cfRule type="duplicateValues" dxfId="1279" priority="1280"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B12">
+    <cfRule type="duplicateValues" dxfId="1279" priority="1216"/>
+    <cfRule type="duplicateValues" dxfId="1278" priority="1279"/>
+    <cfRule type="duplicateValues" dxfId="1277" priority="1278"/>
+    <cfRule type="duplicateValues" dxfId="1276" priority="1277"/>
+    <cfRule type="duplicateValues" dxfId="1275" priority="1276"/>
+    <cfRule type="duplicateValues" dxfId="1274" priority="1275"/>
+    <cfRule type="duplicateValues" dxfId="1273" priority="1274"/>
+    <cfRule type="duplicateValues" dxfId="1272" priority="1273"/>
+    <cfRule type="duplicateValues" dxfId="1271" priority="1272"/>
+    <cfRule type="duplicateValues" dxfId="1270" priority="1271"/>
+    <cfRule type="duplicateValues" dxfId="1269" priority="1270"/>
+    <cfRule type="duplicateValues" dxfId="1268" priority="1269"/>
+    <cfRule type="duplicateValues" dxfId="1267" priority="1268"/>
+    <cfRule type="duplicateValues" dxfId="1266" priority="1267"/>
+    <cfRule type="duplicateValues" dxfId="1265" priority="1266"/>
+    <cfRule type="duplicateValues" dxfId="1264" priority="1265"/>
+    <cfRule type="duplicateValues" dxfId="1263" priority="1264"/>
+    <cfRule type="duplicateValues" dxfId="1262" priority="1263"/>
+    <cfRule type="duplicateValues" dxfId="1261" priority="1262"/>
+    <cfRule type="duplicateValues" dxfId="1260" priority="1261"/>
+    <cfRule type="duplicateValues" dxfId="1259" priority="1260"/>
+    <cfRule type="duplicateValues" dxfId="1258" priority="1259"/>
+    <cfRule type="duplicateValues" dxfId="1257" priority="1258"/>
+    <cfRule type="duplicateValues" dxfId="1256" priority="1257"/>
+    <cfRule type="duplicateValues" dxfId="1255" priority="1256"/>
+    <cfRule type="duplicateValues" dxfId="1254" priority="1255"/>
+    <cfRule type="duplicateValues" dxfId="1253" priority="1254"/>
+    <cfRule type="duplicateValues" dxfId="1252" priority="1253"/>
+    <cfRule type="duplicateValues" dxfId="1251" priority="1252"/>
+    <cfRule type="duplicateValues" dxfId="1250" priority="1251"/>
+    <cfRule type="duplicateValues" dxfId="1249" priority="1250"/>
+    <cfRule type="duplicateValues" dxfId="1248" priority="1249"/>
+    <cfRule type="duplicateValues" dxfId="1247" priority="1248"/>
+    <cfRule type="duplicateValues" dxfId="1246" priority="1247"/>
+    <cfRule type="duplicateValues" dxfId="1245" priority="1246"/>
+    <cfRule type="duplicateValues" dxfId="1244" priority="1245"/>
+    <cfRule type="duplicateValues" dxfId="1243" priority="1244"/>
+    <cfRule type="duplicateValues" dxfId="1242" priority="1243"/>
+    <cfRule type="duplicateValues" dxfId="1241" priority="1242"/>
+    <cfRule type="duplicateValues" dxfId="1240" priority="1241"/>
+    <cfRule type="duplicateValues" dxfId="1239" priority="1240"/>
+    <cfRule type="duplicateValues" dxfId="1238" priority="1239"/>
+    <cfRule type="duplicateValues" dxfId="1237" priority="1238"/>
+    <cfRule type="duplicateValues" dxfId="1236" priority="1237"/>
+    <cfRule type="duplicateValues" dxfId="1235" priority="1236"/>
+    <cfRule type="duplicateValues" dxfId="1234" priority="1235"/>
+    <cfRule type="duplicateValues" dxfId="1233" priority="1234"/>
+    <cfRule type="duplicateValues" dxfId="1232" priority="1233"/>
+    <cfRule type="duplicateValues" dxfId="1231" priority="1232"/>
+    <cfRule type="duplicateValues" dxfId="1230" priority="1231"/>
+    <cfRule type="duplicateValues" dxfId="1229" priority="1230"/>
+    <cfRule type="duplicateValues" dxfId="1228" priority="1229"/>
+    <cfRule type="duplicateValues" dxfId="1227" priority="1228"/>
+    <cfRule type="duplicateValues" dxfId="1226" priority="1227"/>
+    <cfRule type="duplicateValues" dxfId="1225" priority="1226"/>
+    <cfRule type="duplicateValues" dxfId="1224" priority="1225"/>
+    <cfRule type="duplicateValues" dxfId="1223" priority="1224"/>
+    <cfRule type="duplicateValues" dxfId="1222" priority="1223"/>
+    <cfRule type="duplicateValues" dxfId="1221" priority="1222"/>
+    <cfRule type="duplicateValues" dxfId="1220" priority="1221"/>
+    <cfRule type="duplicateValues" dxfId="1219" priority="1220"/>
+    <cfRule type="duplicateValues" dxfId="1218" priority="1219"/>
+    <cfRule type="duplicateValues" dxfId="1217" priority="1218"/>
+    <cfRule type="duplicateValues" dxfId="1216" priority="1217"/>
+    <cfRule type="duplicateValues" dxfId="1215" priority="1152"/>
+    <cfRule type="duplicateValues" dxfId="1214" priority="1215"/>
+    <cfRule type="duplicateValues" dxfId="1213" priority="1214"/>
+    <cfRule type="duplicateValues" dxfId="1212" priority="1213"/>
+    <cfRule type="duplicateValues" dxfId="1211" priority="1212"/>
+    <cfRule type="duplicateValues" dxfId="1210" priority="1211"/>
+    <cfRule type="duplicateValues" dxfId="1209" priority="1210"/>
+    <cfRule type="duplicateValues" dxfId="1208" priority="1209"/>
+    <cfRule type="duplicateValues" dxfId="1207" priority="1208"/>
+    <cfRule type="duplicateValues" dxfId="1206" priority="1207"/>
+    <cfRule type="duplicateValues" dxfId="1205" priority="1206"/>
+    <cfRule type="duplicateValues" dxfId="1204" priority="1205"/>
+    <cfRule type="duplicateValues" dxfId="1203" priority="1204"/>
+    <cfRule type="duplicateValues" dxfId="1202" priority="1203"/>
+    <cfRule type="duplicateValues" dxfId="1201" priority="1202"/>
+    <cfRule type="duplicateValues" dxfId="1200" priority="1201"/>
+    <cfRule type="duplicateValues" dxfId="1199" priority="1200"/>
+    <cfRule type="duplicateValues" dxfId="1198" priority="1199"/>
+    <cfRule type="duplicateValues" dxfId="1197" priority="1198"/>
+    <cfRule type="duplicateValues" dxfId="1196" priority="1197"/>
+    <cfRule type="duplicateValues" dxfId="1195" priority="1196"/>
+    <cfRule type="duplicateValues" dxfId="1194" priority="1195"/>
+    <cfRule type="duplicateValues" dxfId="1193" priority="1194"/>
+    <cfRule type="duplicateValues" dxfId="1192" priority="1193"/>
+    <cfRule type="duplicateValues" dxfId="1191" priority="1192"/>
+    <cfRule type="duplicateValues" dxfId="1190" priority="1191"/>
+    <cfRule type="duplicateValues" dxfId="1189" priority="1190"/>
+    <cfRule type="duplicateValues" dxfId="1188" priority="1189"/>
+    <cfRule type="duplicateValues" dxfId="1187" priority="1188"/>
+    <cfRule type="duplicateValues" dxfId="1186" priority="1187"/>
+    <cfRule type="duplicateValues" dxfId="1185" priority="1186"/>
+    <cfRule type="duplicateValues" dxfId="1184" priority="1185"/>
+    <cfRule type="duplicateValues" dxfId="1183" priority="1184"/>
+    <cfRule type="duplicateValues" dxfId="1182" priority="1183"/>
+    <cfRule type="duplicateValues" dxfId="1181" priority="1182"/>
+    <cfRule type="duplicateValues" dxfId="1180" priority="1181"/>
+    <cfRule type="duplicateValues" dxfId="1179" priority="1180"/>
+    <cfRule type="duplicateValues" dxfId="1178" priority="1179"/>
+    <cfRule type="duplicateValues" dxfId="1177" priority="1178"/>
+    <cfRule type="duplicateValues" dxfId="1176" priority="1177"/>
+    <cfRule type="duplicateValues" dxfId="1175" priority="1176"/>
+    <cfRule type="duplicateValues" dxfId="1174" priority="1175"/>
+    <cfRule type="duplicateValues" dxfId="1173" priority="1174"/>
+    <cfRule type="duplicateValues" dxfId="1172" priority="1173"/>
+    <cfRule type="duplicateValues" dxfId="1171" priority="1172"/>
+    <cfRule type="duplicateValues" dxfId="1170" priority="1171"/>
+    <cfRule type="duplicateValues" dxfId="1169" priority="1170"/>
+    <cfRule type="duplicateValues" dxfId="1168" priority="1169"/>
+    <cfRule type="duplicateValues" dxfId="1167" priority="1168"/>
+    <cfRule type="duplicateValues" dxfId="1166" priority="1167"/>
+    <cfRule type="duplicateValues" dxfId="1165" priority="1166"/>
+    <cfRule type="duplicateValues" dxfId="1164" priority="1165"/>
+    <cfRule type="duplicateValues" dxfId="1163" priority="1164"/>
+    <cfRule type="duplicateValues" dxfId="1162" priority="1163"/>
+    <cfRule type="duplicateValues" dxfId="1161" priority="1162"/>
+    <cfRule type="duplicateValues" dxfId="1160" priority="1161"/>
+    <cfRule type="duplicateValues" dxfId="1159" priority="1160"/>
+    <cfRule type="duplicateValues" dxfId="1158" priority="1159"/>
+    <cfRule type="duplicateValues" dxfId="1157" priority="1158"/>
+    <cfRule type="duplicateValues" dxfId="1156" priority="1157"/>
+    <cfRule type="duplicateValues" dxfId="1155" priority="1156"/>
+    <cfRule type="duplicateValues" dxfId="1154" priority="1155"/>
+    <cfRule type="duplicateValues" dxfId="1153" priority="1154"/>
+    <cfRule type="duplicateValues" dxfId="1152" priority="1153"/>
+    <cfRule type="duplicateValues" dxfId="1151" priority="1120"/>
+    <cfRule type="duplicateValues" dxfId="1150" priority="1151"/>
+    <cfRule type="duplicateValues" dxfId="1149" priority="1150"/>
+    <cfRule type="duplicateValues" dxfId="1148" priority="1149"/>
+    <cfRule type="duplicateValues" dxfId="1147" priority="1148"/>
+    <cfRule type="duplicateValues" dxfId="1146" priority="1147"/>
+    <cfRule type="duplicateValues" dxfId="1145" priority="1146"/>
+    <cfRule type="duplicateValues" dxfId="1144" priority="1145"/>
+    <cfRule type="duplicateValues" dxfId="1143" priority="1144"/>
+    <cfRule type="duplicateValues" dxfId="1142" priority="1143"/>
+    <cfRule type="duplicateValues" dxfId="1141" priority="1142"/>
+    <cfRule type="duplicateValues" dxfId="1140" priority="1141"/>
+    <cfRule type="duplicateValues" dxfId="1139" priority="1140"/>
+    <cfRule type="duplicateValues" dxfId="1138" priority="1139"/>
+    <cfRule type="duplicateValues" dxfId="1137" priority="1138"/>
+    <cfRule type="duplicateValues" dxfId="1136" priority="1137"/>
+    <cfRule type="duplicateValues" dxfId="1135" priority="1136"/>
+    <cfRule type="duplicateValues" dxfId="1134" priority="1135"/>
+    <cfRule type="duplicateValues" dxfId="1133" priority="1134"/>
+    <cfRule type="duplicateValues" dxfId="1132" priority="1133"/>
+    <cfRule type="duplicateValues" dxfId="1131" priority="1132"/>
+    <cfRule type="duplicateValues" dxfId="1130" priority="1131"/>
+    <cfRule type="duplicateValues" dxfId="1129" priority="1130"/>
+    <cfRule type="duplicateValues" dxfId="1128" priority="1129"/>
+    <cfRule type="duplicateValues" dxfId="1127" priority="1128"/>
+    <cfRule type="duplicateValues" dxfId="1126" priority="1127"/>
+    <cfRule type="duplicateValues" dxfId="1125" priority="1126"/>
+    <cfRule type="duplicateValues" dxfId="1124" priority="1125"/>
+    <cfRule type="duplicateValues" dxfId="1123" priority="1124"/>
+    <cfRule type="duplicateValues" dxfId="1122" priority="1123"/>
+    <cfRule type="duplicateValues" dxfId="1121" priority="1122"/>
+    <cfRule type="duplicateValues" dxfId="1120" priority="1121"/>
+    <cfRule type="duplicateValues" dxfId="1119" priority="1280"/>
+    <cfRule type="duplicateValues" dxfId="1118" priority="1119"/>
+    <cfRule type="duplicateValues" dxfId="1117" priority="1118"/>
+    <cfRule type="duplicateValues" dxfId="1116" priority="1117"/>
+    <cfRule type="duplicateValues" dxfId="1115" priority="1116"/>
+    <cfRule type="duplicateValues" dxfId="1114" priority="1115"/>
+    <cfRule type="duplicateValues" dxfId="1113" priority="1114"/>
+    <cfRule type="duplicateValues" dxfId="1112" priority="1113"/>
+    <cfRule type="duplicateValues" dxfId="1111" priority="1112"/>
+    <cfRule type="duplicateValues" dxfId="1110" priority="1111"/>
+    <cfRule type="duplicateValues" dxfId="1109" priority="1110"/>
+    <cfRule type="duplicateValues" dxfId="1108" priority="1109"/>
+    <cfRule type="duplicateValues" dxfId="1107" priority="1108"/>
+    <cfRule type="duplicateValues" dxfId="1106" priority="1107"/>
+    <cfRule type="duplicateValues" dxfId="1105" priority="1106"/>
+    <cfRule type="duplicateValues" dxfId="1104" priority="1105"/>
+    <cfRule type="duplicateValues" dxfId="1103" priority="1104"/>
+    <cfRule type="duplicateValues" dxfId="1102" priority="1103"/>
+    <cfRule type="duplicateValues" dxfId="1101" priority="1102"/>
+    <cfRule type="duplicateValues" dxfId="1100" priority="1101"/>
+    <cfRule type="duplicateValues" dxfId="1099" priority="1100"/>
+    <cfRule type="duplicateValues" dxfId="1098" priority="1099"/>
+    <cfRule type="duplicateValues" dxfId="1097" priority="1098"/>
+    <cfRule type="duplicateValues" dxfId="1096" priority="1097"/>
+    <cfRule type="duplicateValues" dxfId="1095" priority="1096"/>
+    <cfRule type="duplicateValues" dxfId="1094" priority="1095"/>
+    <cfRule type="duplicateValues" dxfId="1093" priority="1094"/>
+    <cfRule type="duplicateValues" dxfId="1092" priority="1093"/>
+    <cfRule type="duplicateValues" dxfId="1091" priority="1092"/>
+    <cfRule type="duplicateValues" dxfId="1090" priority="1091"/>
+    <cfRule type="duplicateValues" dxfId="1089" priority="1090"/>
+    <cfRule type="duplicateValues" dxfId="1088" priority="1089"/>
+    <cfRule type="duplicateValues" dxfId="1087" priority="1088"/>
+    <cfRule type="duplicateValues" dxfId="1086" priority="1087"/>
+    <cfRule type="duplicateValues" dxfId="1085" priority="1086"/>
+    <cfRule type="duplicateValues" dxfId="1084" priority="1085"/>
+    <cfRule type="duplicateValues" dxfId="1083" priority="1084"/>
+    <cfRule type="duplicateValues" dxfId="1082" priority="1083"/>
+    <cfRule type="duplicateValues" dxfId="1081" priority="1082"/>
+    <cfRule type="duplicateValues" dxfId="1080" priority="1081"/>
+    <cfRule type="duplicateValues" dxfId="1079" priority="1080"/>
+    <cfRule type="duplicateValues" dxfId="1078" priority="1079"/>
+    <cfRule type="duplicateValues" dxfId="1077" priority="1078"/>
+    <cfRule type="duplicateValues" dxfId="1076" priority="1077"/>
+    <cfRule type="duplicateValues" dxfId="1075" priority="1076"/>
+    <cfRule type="duplicateValues" dxfId="1074" priority="1075"/>
+    <cfRule type="duplicateValues" dxfId="1073" priority="1074"/>
+    <cfRule type="duplicateValues" dxfId="1072" priority="1073"/>
+    <cfRule type="duplicateValues" dxfId="1071" priority="1072"/>
+    <cfRule type="duplicateValues" dxfId="1070" priority="1071"/>
+    <cfRule type="duplicateValues" dxfId="1069" priority="1070"/>
+    <cfRule type="duplicateValues" dxfId="1068" priority="1069"/>
+    <cfRule type="duplicateValues" dxfId="1067" priority="1068"/>
+    <cfRule type="duplicateValues" dxfId="1066" priority="1067"/>
+    <cfRule type="duplicateValues" dxfId="1065" priority="1066"/>
+    <cfRule type="duplicateValues" dxfId="1064" priority="1065"/>
+    <cfRule type="duplicateValues" dxfId="1063" priority="1064"/>
+    <cfRule type="duplicateValues" dxfId="1062" priority="1063"/>
+    <cfRule type="duplicateValues" dxfId="1061" priority="1062"/>
+    <cfRule type="duplicateValues" dxfId="1060" priority="1061"/>
+    <cfRule type="duplicateValues" dxfId="1059" priority="1060"/>
+    <cfRule type="duplicateValues" dxfId="1058" priority="1059"/>
+    <cfRule type="duplicateValues" dxfId="1057" priority="1058"/>
+    <cfRule type="duplicateValues" dxfId="1056" priority="1057"/>
+    <cfRule type="duplicateValues" dxfId="1055" priority="1056"/>
+    <cfRule type="duplicateValues" dxfId="1054" priority="1055"/>
+    <cfRule type="duplicateValues" dxfId="1053" priority="1054"/>
+    <cfRule type="duplicateValues" dxfId="1052" priority="1053"/>
+    <cfRule type="duplicateValues" dxfId="1051" priority="1052"/>
+    <cfRule type="duplicateValues" dxfId="1050" priority="1051"/>
+    <cfRule type="duplicateValues" dxfId="1049" priority="1050"/>
+    <cfRule type="duplicateValues" dxfId="1048" priority="1049"/>
+    <cfRule type="duplicateValues" dxfId="1047" priority="1048"/>
+    <cfRule type="duplicateValues" dxfId="1046" priority="1047"/>
+    <cfRule type="duplicateValues" dxfId="1045" priority="1046"/>
+    <cfRule type="duplicateValues" dxfId="1044" priority="1045"/>
+    <cfRule type="duplicateValues" dxfId="1043" priority="1044"/>
+    <cfRule type="duplicateValues" dxfId="1042" priority="1043"/>
+    <cfRule type="duplicateValues" dxfId="1041" priority="1042"/>
+    <cfRule type="duplicateValues" dxfId="1040" priority="1041"/>
+    <cfRule type="duplicateValues" dxfId="1039" priority="1040"/>
+    <cfRule type="duplicateValues" dxfId="1038" priority="1039"/>
+    <cfRule type="duplicateValues" dxfId="1037" priority="1038"/>
+    <cfRule type="duplicateValues" dxfId="1036" priority="1037"/>
+    <cfRule type="duplicateValues" dxfId="1035" priority="1036"/>
+    <cfRule type="duplicateValues" dxfId="1034" priority="1035"/>
+    <cfRule type="duplicateValues" dxfId="1033" priority="1034"/>
+    <cfRule type="duplicateValues" dxfId="1032" priority="1033"/>
+    <cfRule type="duplicateValues" dxfId="1031" priority="1032"/>
+    <cfRule type="duplicateValues" dxfId="1030" priority="1031"/>
+    <cfRule type="duplicateValues" dxfId="1029" priority="1030"/>
+    <cfRule type="duplicateValues" dxfId="1028" priority="1029"/>
+    <cfRule type="duplicateValues" dxfId="1027" priority="1028"/>
+    <cfRule type="duplicateValues" dxfId="1026" priority="1027"/>
+    <cfRule type="duplicateValues" dxfId="1025" priority="1026"/>
     <cfRule type="duplicateValues" dxfId="1024" priority="1025"/>
-    <cfRule type="duplicateValues" dxfId="1025" priority="1026"/>
-    <cfRule type="duplicateValues" dxfId="1026" priority="1027"/>
-    <cfRule type="duplicateValues" dxfId="1027" priority="1028"/>
-    <cfRule type="duplicateValues" dxfId="1028" priority="1029"/>
-    <cfRule type="duplicateValues" dxfId="1029" priority="1030"/>
-    <cfRule type="duplicateValues" dxfId="1030" priority="1031"/>
-    <cfRule type="duplicateValues" dxfId="1031" priority="1032"/>
-    <cfRule type="duplicateValues" dxfId="1032" priority="1033"/>
-    <cfRule type="duplicateValues" dxfId="1033" priority="1034"/>
-    <cfRule type="duplicateValues" dxfId="1034" priority="1035"/>
-    <cfRule type="duplicateValues" dxfId="1035" priority="1036"/>
-    <cfRule type="duplicateValues" dxfId="1036" priority="1037"/>
-    <cfRule type="duplicateValues" dxfId="1037" priority="1038"/>
-    <cfRule type="duplicateValues" dxfId="1038" priority="1039"/>
-    <cfRule type="duplicateValues" dxfId="1039" priority="1040"/>
-    <cfRule type="duplicateValues" dxfId="1040" priority="1041"/>
-    <cfRule type="duplicateValues" dxfId="1041" priority="1042"/>
-    <cfRule type="duplicateValues" dxfId="1042" priority="1043"/>
-    <cfRule type="duplicateValues" dxfId="1043" priority="1044"/>
-    <cfRule type="duplicateValues" dxfId="1044" priority="1045"/>
-    <cfRule type="duplicateValues" dxfId="1045" priority="1046"/>
-    <cfRule type="duplicateValues" dxfId="1046" priority="1047"/>
-    <cfRule type="duplicateValues" dxfId="1047" priority="1048"/>
-    <cfRule type="duplicateValues" dxfId="1048" priority="1049"/>
-    <cfRule type="duplicateValues" dxfId="1049" priority="1050"/>
-    <cfRule type="duplicateValues" dxfId="1050" priority="1051"/>
-    <cfRule type="duplicateValues" dxfId="1051" priority="1052"/>
-    <cfRule type="duplicateValues" dxfId="1052" priority="1053"/>
-    <cfRule type="duplicateValues" dxfId="1053" priority="1054"/>
-    <cfRule type="duplicateValues" dxfId="1054" priority="1055"/>
-    <cfRule type="duplicateValues" dxfId="1055" priority="1056"/>
-    <cfRule type="duplicateValues" dxfId="1056" priority="1057"/>
-    <cfRule type="duplicateValues" dxfId="1057" priority="1058"/>
-    <cfRule type="duplicateValues" dxfId="1058" priority="1059"/>
-    <cfRule type="duplicateValues" dxfId="1059" priority="1060"/>
-    <cfRule type="duplicateValues" dxfId="1060" priority="1061"/>
-    <cfRule type="duplicateValues" dxfId="1061" priority="1062"/>
-    <cfRule type="duplicateValues" dxfId="1062" priority="1063"/>
-    <cfRule type="duplicateValues" dxfId="1063" priority="1064"/>
-    <cfRule type="duplicateValues" dxfId="1064" priority="1065"/>
-    <cfRule type="duplicateValues" dxfId="1065" priority="1066"/>
-    <cfRule type="duplicateValues" dxfId="1066" priority="1067"/>
-    <cfRule type="duplicateValues" dxfId="1067" priority="1068"/>
-    <cfRule type="duplicateValues" dxfId="1068" priority="1069"/>
-    <cfRule type="duplicateValues" dxfId="1069" priority="1070"/>
-    <cfRule type="duplicateValues" dxfId="1070" priority="1071"/>
-    <cfRule type="duplicateValues" dxfId="1071" priority="1072"/>
-    <cfRule type="duplicateValues" dxfId="1072" priority="1073"/>
-    <cfRule type="duplicateValues" dxfId="1073" priority="1074"/>
-    <cfRule type="duplicateValues" dxfId="1074" priority="1075"/>
-    <cfRule type="duplicateValues" dxfId="1075" priority="1076"/>
-    <cfRule type="duplicateValues" dxfId="1076" priority="1077"/>
-    <cfRule type="duplicateValues" dxfId="1077" priority="1078"/>
-    <cfRule type="duplicateValues" dxfId="1078" priority="1079"/>
-    <cfRule type="duplicateValues" dxfId="1079" priority="1080"/>
-    <cfRule type="duplicateValues" dxfId="1080" priority="1081"/>
-    <cfRule type="duplicateValues" dxfId="1081" priority="1082"/>
-    <cfRule type="duplicateValues" dxfId="1082" priority="1083"/>
-    <cfRule type="duplicateValues" dxfId="1083" priority="1084"/>
-    <cfRule type="duplicateValues" dxfId="1084" priority="1085"/>
-    <cfRule type="duplicateValues" dxfId="1085" priority="1086"/>
-    <cfRule type="duplicateValues" dxfId="1086" priority="1087"/>
-    <cfRule type="duplicateValues" dxfId="1150" priority="1088"/>
-    <cfRule type="duplicateValues" dxfId="1087" priority="1089"/>
-    <cfRule type="duplicateValues" dxfId="1088" priority="1090"/>
-    <cfRule type="duplicateValues" dxfId="1089" priority="1091"/>
-    <cfRule type="duplicateValues" dxfId="1090" priority="1092"/>
-    <cfRule type="duplicateValues" dxfId="1091" priority="1093"/>
-    <cfRule type="duplicateValues" dxfId="1092" priority="1094"/>
-    <cfRule type="duplicateValues" dxfId="1093" priority="1095"/>
-    <cfRule type="duplicateValues" dxfId="1094" priority="1096"/>
-    <cfRule type="duplicateValues" dxfId="1095" priority="1097"/>
-    <cfRule type="duplicateValues" dxfId="1096" priority="1098"/>
-    <cfRule type="duplicateValues" dxfId="1097" priority="1099"/>
-    <cfRule type="duplicateValues" dxfId="1098" priority="1100"/>
-    <cfRule type="duplicateValues" dxfId="1099" priority="1101"/>
-    <cfRule type="duplicateValues" dxfId="1100" priority="1102"/>
-    <cfRule type="duplicateValues" dxfId="1101" priority="1103"/>
-    <cfRule type="duplicateValues" dxfId="1102" priority="1104"/>
-    <cfRule type="duplicateValues" dxfId="1103" priority="1105"/>
-    <cfRule type="duplicateValues" dxfId="1104" priority="1106"/>
-    <cfRule type="duplicateValues" dxfId="1105" priority="1107"/>
-    <cfRule type="duplicateValues" dxfId="1106" priority="1108"/>
-    <cfRule type="duplicateValues" dxfId="1107" priority="1109"/>
-    <cfRule type="duplicateValues" dxfId="1108" priority="1110"/>
-    <cfRule type="duplicateValues" dxfId="1109" priority="1111"/>
-    <cfRule type="duplicateValues" dxfId="1110" priority="1112"/>
-    <cfRule type="duplicateValues" dxfId="1111" priority="1113"/>
-    <cfRule type="duplicateValues" dxfId="1112" priority="1114"/>
-    <cfRule type="duplicateValues" dxfId="1113" priority="1115"/>
-    <cfRule type="duplicateValues" dxfId="1114" priority="1116"/>
-    <cfRule type="duplicateValues" dxfId="1115" priority="1117"/>
-    <cfRule type="duplicateValues" dxfId="1116" priority="1118"/>
-    <cfRule type="duplicateValues" dxfId="1117" priority="1119"/>
-    <cfRule type="duplicateValues" dxfId="1118" priority="1120"/>
-    <cfRule type="duplicateValues" dxfId="1119" priority="1121"/>
-    <cfRule type="duplicateValues" dxfId="1120" priority="1122"/>
-    <cfRule type="duplicateValues" dxfId="1121" priority="1123"/>
-    <cfRule type="duplicateValues" dxfId="1122" priority="1124"/>
-    <cfRule type="duplicateValues" dxfId="1123" priority="1125"/>
-    <cfRule type="duplicateValues" dxfId="1124" priority="1126"/>
-    <cfRule type="duplicateValues" dxfId="1125" priority="1127"/>
-    <cfRule type="duplicateValues" dxfId="1126" priority="1128"/>
-    <cfRule type="duplicateValues" dxfId="1127" priority="1129"/>
-    <cfRule type="duplicateValues" dxfId="1128" priority="1130"/>
-    <cfRule type="duplicateValues" dxfId="1129" priority="1131"/>
-    <cfRule type="duplicateValues" dxfId="1130" priority="1132"/>
-    <cfRule type="duplicateValues" dxfId="1131" priority="1133"/>
-    <cfRule type="duplicateValues" dxfId="1132" priority="1134"/>
-    <cfRule type="duplicateValues" dxfId="1133" priority="1135"/>
-    <cfRule type="duplicateValues" dxfId="1134" priority="1136"/>
-    <cfRule type="duplicateValues" dxfId="1135" priority="1137"/>
-    <cfRule type="duplicateValues" dxfId="1136" priority="1138"/>
-    <cfRule type="duplicateValues" dxfId="1137" priority="1139"/>
-    <cfRule type="duplicateValues" dxfId="1138" priority="1140"/>
-    <cfRule type="duplicateValues" dxfId="1139" priority="1141"/>
-    <cfRule type="duplicateValues" dxfId="1140" priority="1142"/>
-    <cfRule type="duplicateValues" dxfId="1141" priority="1143"/>
-    <cfRule type="duplicateValues" dxfId="1142" priority="1144"/>
-    <cfRule type="duplicateValues" dxfId="1143" priority="1145"/>
-    <cfRule type="duplicateValues" dxfId="1144" priority="1146"/>
-    <cfRule type="duplicateValues" dxfId="1145" priority="1147"/>
-    <cfRule type="duplicateValues" dxfId="1146" priority="1148"/>
-    <cfRule type="duplicateValues" dxfId="1147" priority="1149"/>
-    <cfRule type="duplicateValues" dxfId="1148" priority="1150"/>
-    <cfRule type="duplicateValues" dxfId="1149" priority="1151"/>
-    <cfRule type="duplicateValues" dxfId="1214" priority="1152"/>
-    <cfRule type="duplicateValues" dxfId="1151" priority="1153"/>
-    <cfRule type="duplicateValues" dxfId="1152" priority="1154"/>
-    <cfRule type="duplicateValues" dxfId="1153" priority="1155"/>
-    <cfRule type="duplicateValues" dxfId="1154" priority="1156"/>
-    <cfRule type="duplicateValues" dxfId="1155" priority="1157"/>
-    <cfRule type="duplicateValues" dxfId="1156" priority="1158"/>
-    <cfRule type="duplicateValues" dxfId="1157" priority="1159"/>
-    <cfRule type="duplicateValues" dxfId="1158" priority="1160"/>
-    <cfRule type="duplicateValues" dxfId="1159" priority="1161"/>
-    <cfRule type="duplicateValues" dxfId="1160" priority="1162"/>
-    <cfRule type="duplicateValues" dxfId="1161" priority="1163"/>
-    <cfRule type="duplicateValues" dxfId="1162" priority="1164"/>
-    <cfRule type="duplicateValues" dxfId="1163" priority="1165"/>
-    <cfRule type="duplicateValues" dxfId="1164" priority="1166"/>
-    <cfRule type="duplicateValues" dxfId="1165" priority="1167"/>
-    <cfRule type="duplicateValues" dxfId="1166" priority="1168"/>
-    <cfRule type="duplicateValues" dxfId="1167" priority="1169"/>
-    <cfRule type="duplicateValues" dxfId="1168" priority="1170"/>
-    <cfRule type="duplicateValues" dxfId="1169" priority="1171"/>
-    <cfRule type="duplicateValues" dxfId="1170" priority="1172"/>
-    <cfRule type="duplicateValues" dxfId="1171" priority="1173"/>
-    <cfRule type="duplicateValues" dxfId="1172" priority="1174"/>
-    <cfRule type="duplicateValues" dxfId="1173" priority="1175"/>
-    <cfRule type="duplicateValues" dxfId="1174" priority="1176"/>
-    <cfRule type="duplicateValues" dxfId="1175" priority="1177"/>
-    <cfRule type="duplicateValues" dxfId="1176" priority="1178"/>
-    <cfRule type="duplicateValues" dxfId="1177" priority="1179"/>
-    <cfRule type="duplicateValues" dxfId="1178" priority="1180"/>
-    <cfRule type="duplicateValues" dxfId="1179" priority="1181"/>
-    <cfRule type="duplicateValues" dxfId="1180" priority="1182"/>
-    <cfRule type="duplicateValues" dxfId="1181" priority="1183"/>
-    <cfRule type="duplicateValues" dxfId="1182" priority="1184"/>
-    <cfRule type="duplicateValues" dxfId="1183" priority="1185"/>
-    <cfRule type="duplicateValues" dxfId="1184" priority="1186"/>
-    <cfRule type="duplicateValues" dxfId="1185" priority="1187"/>
-    <cfRule type="duplicateValues" dxfId="1186" priority="1188"/>
-    <cfRule type="duplicateValues" dxfId="1187" priority="1189"/>
-    <cfRule type="duplicateValues" dxfId="1188" priority="1190"/>
-    <cfRule type="duplicateValues" dxfId="1189" priority="1191"/>
-    <cfRule type="duplicateValues" dxfId="1190" priority="1192"/>
-    <cfRule type="duplicateValues" dxfId="1191" priority="1193"/>
-    <cfRule type="duplicateValues" dxfId="1192" priority="1194"/>
-    <cfRule type="duplicateValues" dxfId="1193" priority="1195"/>
-    <cfRule type="duplicateValues" dxfId="1194" priority="1196"/>
-    <cfRule type="duplicateValues" dxfId="1195" priority="1197"/>
-    <cfRule type="duplicateValues" dxfId="1196" priority="1198"/>
-    <cfRule type="duplicateValues" dxfId="1197" priority="1199"/>
-    <cfRule type="duplicateValues" dxfId="1198" priority="1200"/>
-    <cfRule type="duplicateValues" dxfId="1199" priority="1201"/>
-    <cfRule type="duplicateValues" dxfId="1200" priority="1202"/>
-    <cfRule type="duplicateValues" dxfId="1201" priority="1203"/>
-    <cfRule type="duplicateValues" dxfId="1202" priority="1204"/>
-    <cfRule type="duplicateValues" dxfId="1203" priority="1205"/>
-    <cfRule type="duplicateValues" dxfId="1204" priority="1206"/>
-    <cfRule type="duplicateValues" dxfId="1205" priority="1207"/>
-    <cfRule type="duplicateValues" dxfId="1206" priority="1208"/>
-    <cfRule type="duplicateValues" dxfId="1207" priority="1209"/>
-    <cfRule type="duplicateValues" dxfId="1208" priority="1210"/>
-    <cfRule type="duplicateValues" dxfId="1209" priority="1211"/>
-    <cfRule type="duplicateValues" dxfId="1210" priority="1212"/>
-    <cfRule type="duplicateValues" dxfId="1211" priority="1213"/>
-    <cfRule type="duplicateValues" dxfId="1212" priority="1214"/>
-    <cfRule type="duplicateValues" dxfId="1213" priority="1215"/>
-    <cfRule type="duplicateValues" dxfId="1278" priority="1216"/>
-    <cfRule type="duplicateValues" dxfId="1215" priority="1217"/>
-    <cfRule type="duplicateValues" dxfId="1216" priority="1218"/>
-    <cfRule type="duplicateValues" dxfId="1217" priority="1219"/>
-    <cfRule type="duplicateValues" dxfId="1218" priority="1220"/>
-    <cfRule type="duplicateValues" dxfId="1219" priority="1221"/>
-    <cfRule type="duplicateValues" dxfId="1220" priority="1222"/>
-    <cfRule type="duplicateValues" dxfId="1221" priority="1223"/>
-    <cfRule type="duplicateValues" dxfId="1222" priority="1224"/>
-    <cfRule type="duplicateValues" dxfId="1223" priority="1225"/>
-    <cfRule type="duplicateValues" dxfId="1224" priority="1226"/>
-    <cfRule type="duplicateValues" dxfId="1225" priority="1227"/>
-    <cfRule type="duplicateValues" dxfId="1226" priority="1228"/>
-    <cfRule type="duplicateValues" dxfId="1227" priority="1229"/>
-    <cfRule type="duplicateValues" dxfId="1228" priority="1230"/>
-    <cfRule type="duplicateValues" dxfId="1229" priority="1231"/>
-    <cfRule type="duplicateValues" dxfId="1230" priority="1232"/>
-    <cfRule type="duplicateValues" dxfId="1231" priority="1233"/>
-    <cfRule type="duplicateValues" dxfId="1232" priority="1234"/>
-    <cfRule type="duplicateValues" dxfId="1233" priority="1235"/>
-    <cfRule type="duplicateValues" dxfId="1234" priority="1236"/>
-    <cfRule type="duplicateValues" dxfId="1235" priority="1237"/>
-    <cfRule type="duplicateValues" dxfId="1236" priority="1238"/>
-    <cfRule type="duplicateValues" dxfId="1237" priority="1239"/>
-    <cfRule type="duplicateValues" dxfId="1238" priority="1240"/>
-    <cfRule type="duplicateValues" dxfId="1239" priority="1241"/>
-    <cfRule type="duplicateValues" dxfId="1240" priority="1242"/>
-    <cfRule type="duplicateValues" dxfId="1241" priority="1243"/>
-    <cfRule type="duplicateValues" dxfId="1242" priority="1244"/>
-    <cfRule type="duplicateValues" dxfId="1243" priority="1245"/>
-    <cfRule type="duplicateValues" dxfId="1244" priority="1246"/>
-    <cfRule type="duplicateValues" dxfId="1245" priority="1247"/>
-    <cfRule type="duplicateValues" dxfId="1246" priority="1248"/>
-    <cfRule type="duplicateValues" dxfId="1247" priority="1249"/>
-    <cfRule type="duplicateValues" dxfId="1248" priority="1250"/>
-    <cfRule type="duplicateValues" dxfId="1249" priority="1251"/>
-    <cfRule type="duplicateValues" dxfId="1250" priority="1252"/>
-    <cfRule type="duplicateValues" dxfId="1251" priority="1253"/>
-    <cfRule type="duplicateValues" dxfId="1252" priority="1254"/>
-    <cfRule type="duplicateValues" dxfId="1253" priority="1255"/>
-    <cfRule type="duplicateValues" dxfId="1254" priority="1256"/>
-    <cfRule type="duplicateValues" dxfId="1255" priority="1257"/>
-    <cfRule type="duplicateValues" dxfId="1256" priority="1258"/>
-    <cfRule type="duplicateValues" dxfId="1257" priority="1259"/>
-    <cfRule type="duplicateValues" dxfId="1258" priority="1260"/>
-    <cfRule type="duplicateValues" dxfId="1259" priority="1261"/>
-    <cfRule type="duplicateValues" dxfId="1260" priority="1262"/>
-    <cfRule type="duplicateValues" dxfId="1261" priority="1263"/>
-    <cfRule type="duplicateValues" dxfId="1262" priority="1264"/>
-    <cfRule type="duplicateValues" dxfId="1263" priority="1265"/>
-    <cfRule type="duplicateValues" dxfId="1264" priority="1266"/>
-    <cfRule type="duplicateValues" dxfId="1265" priority="1267"/>
-    <cfRule type="duplicateValues" dxfId="1266" priority="1268"/>
-    <cfRule type="duplicateValues" dxfId="1267" priority="1269"/>
-    <cfRule type="duplicateValues" dxfId="1268" priority="1270"/>
-    <cfRule type="duplicateValues" dxfId="1269" priority="1271"/>
-    <cfRule type="duplicateValues" dxfId="1270" priority="1272"/>
-    <cfRule type="duplicateValues" dxfId="1271" priority="1273"/>
-    <cfRule type="duplicateValues" dxfId="1272" priority="1274"/>
-    <cfRule type="duplicateValues" dxfId="1273" priority="1275"/>
-    <cfRule type="duplicateValues" dxfId="1274" priority="1276"/>
-    <cfRule type="duplicateValues" dxfId="1275" priority="1277"/>
-    <cfRule type="duplicateValues" dxfId="1276" priority="1278"/>
-    <cfRule type="duplicateValues" dxfId="1277" priority="1279"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:B207">
-    <cfRule type="duplicateValues" dxfId="768" priority="769"/>
-    <cfRule type="duplicateValues" dxfId="769" priority="770"/>
-    <cfRule type="duplicateValues" dxfId="770" priority="771"/>
-    <cfRule type="duplicateValues" dxfId="771" priority="772"/>
-    <cfRule type="duplicateValues" dxfId="772" priority="773"/>
-    <cfRule type="duplicateValues" dxfId="773" priority="774"/>
-    <cfRule type="duplicateValues" dxfId="774" priority="775"/>
-    <cfRule type="duplicateValues" dxfId="775" priority="776"/>
-    <cfRule type="duplicateValues" dxfId="776" priority="777"/>
-    <cfRule type="duplicateValues" dxfId="777" priority="778"/>
-    <cfRule type="duplicateValues" dxfId="778" priority="779"/>
-    <cfRule type="duplicateValues" dxfId="779" priority="780"/>
-    <cfRule type="duplicateValues" dxfId="780" priority="781"/>
-    <cfRule type="duplicateValues" dxfId="781" priority="782"/>
-    <cfRule type="duplicateValues" dxfId="782" priority="783"/>
-    <cfRule type="duplicateValues" dxfId="783" priority="784"/>
-    <cfRule type="duplicateValues" dxfId="784" priority="785"/>
-    <cfRule type="duplicateValues" dxfId="785" priority="786"/>
-    <cfRule type="duplicateValues" dxfId="786" priority="787"/>
-    <cfRule type="duplicateValues" dxfId="787" priority="788"/>
-    <cfRule type="duplicateValues" dxfId="788" priority="789"/>
-    <cfRule type="duplicateValues" dxfId="789" priority="790"/>
-    <cfRule type="duplicateValues" dxfId="790" priority="791"/>
-    <cfRule type="duplicateValues" dxfId="791" priority="792"/>
-    <cfRule type="duplicateValues" dxfId="792" priority="793"/>
-    <cfRule type="duplicateValues" dxfId="793" priority="794"/>
-    <cfRule type="duplicateValues" dxfId="794" priority="795"/>
-    <cfRule type="duplicateValues" dxfId="795" priority="796"/>
-    <cfRule type="duplicateValues" dxfId="796" priority="797"/>
-    <cfRule type="duplicateValues" dxfId="797" priority="798"/>
-    <cfRule type="duplicateValues" dxfId="798" priority="799"/>
+    <cfRule type="duplicateValues" dxfId="1023" priority="960"/>
+    <cfRule type="duplicateValues" dxfId="1022" priority="1023"/>
+    <cfRule type="duplicateValues" dxfId="1021" priority="1022"/>
+    <cfRule type="duplicateValues" dxfId="1020" priority="1021"/>
+    <cfRule type="duplicateValues" dxfId="1019" priority="1020"/>
+    <cfRule type="duplicateValues" dxfId="1018" priority="1019"/>
+    <cfRule type="duplicateValues" dxfId="1017" priority="1018"/>
+    <cfRule type="duplicateValues" dxfId="1016" priority="1017"/>
+    <cfRule type="duplicateValues" dxfId="1015" priority="1016"/>
+    <cfRule type="duplicateValues" dxfId="1014" priority="1015"/>
+    <cfRule type="duplicateValues" dxfId="1013" priority="1014"/>
+    <cfRule type="duplicateValues" dxfId="1012" priority="1013"/>
+    <cfRule type="duplicateValues" dxfId="1011" priority="1012"/>
+    <cfRule type="duplicateValues" dxfId="1010" priority="1011"/>
+    <cfRule type="duplicateValues" dxfId="1009" priority="1010"/>
+    <cfRule type="duplicateValues" dxfId="1008" priority="1009"/>
+    <cfRule type="duplicateValues" dxfId="1007" priority="1008"/>
+    <cfRule type="duplicateValues" dxfId="1006" priority="1007"/>
+    <cfRule type="duplicateValues" dxfId="1005" priority="1006"/>
+    <cfRule type="duplicateValues" dxfId="1004" priority="1005"/>
+    <cfRule type="duplicateValues" dxfId="1003" priority="1004"/>
+    <cfRule type="duplicateValues" dxfId="1002" priority="1003"/>
+    <cfRule type="duplicateValues" dxfId="1001" priority="1002"/>
+    <cfRule type="duplicateValues" dxfId="1000" priority="1001"/>
+    <cfRule type="duplicateValues" dxfId="999" priority="1000"/>
+    <cfRule type="duplicateValues" dxfId="998" priority="999"/>
+    <cfRule type="duplicateValues" dxfId="997" priority="998"/>
+    <cfRule type="duplicateValues" dxfId="996" priority="997"/>
+    <cfRule type="duplicateValues" dxfId="995" priority="996"/>
+    <cfRule type="duplicateValues" dxfId="994" priority="995"/>
+    <cfRule type="duplicateValues" dxfId="993" priority="994"/>
+    <cfRule type="duplicateValues" dxfId="992" priority="993"/>
+    <cfRule type="duplicateValues" dxfId="991" priority="992"/>
+    <cfRule type="duplicateValues" dxfId="990" priority="991"/>
+    <cfRule type="duplicateValues" dxfId="989" priority="990"/>
+    <cfRule type="duplicateValues" dxfId="988" priority="989"/>
+    <cfRule type="duplicateValues" dxfId="987" priority="988"/>
+    <cfRule type="duplicateValues" dxfId="986" priority="987"/>
+    <cfRule type="duplicateValues" dxfId="985" priority="986"/>
+    <cfRule type="duplicateValues" dxfId="984" priority="985"/>
+    <cfRule type="duplicateValues" dxfId="983" priority="984"/>
+    <cfRule type="duplicateValues" dxfId="982" priority="983"/>
+    <cfRule type="duplicateValues" dxfId="981" priority="982"/>
+    <cfRule type="duplicateValues" dxfId="980" priority="981"/>
+    <cfRule type="duplicateValues" dxfId="979" priority="980"/>
+    <cfRule type="duplicateValues" dxfId="978" priority="979"/>
+    <cfRule type="duplicateValues" dxfId="977" priority="978"/>
+    <cfRule type="duplicateValues" dxfId="976" priority="977"/>
+    <cfRule type="duplicateValues" dxfId="975" priority="976"/>
+    <cfRule type="duplicateValues" dxfId="974" priority="975"/>
+    <cfRule type="duplicateValues" dxfId="973" priority="974"/>
+    <cfRule type="duplicateValues" dxfId="972" priority="973"/>
+    <cfRule type="duplicateValues" dxfId="971" priority="972"/>
+    <cfRule type="duplicateValues" dxfId="970" priority="971"/>
+    <cfRule type="duplicateValues" dxfId="969" priority="970"/>
+    <cfRule type="duplicateValues" dxfId="968" priority="969"/>
+    <cfRule type="duplicateValues" dxfId="967" priority="968"/>
+    <cfRule type="duplicateValues" dxfId="966" priority="967"/>
+    <cfRule type="duplicateValues" dxfId="965" priority="966"/>
+    <cfRule type="duplicateValues" dxfId="964" priority="965"/>
+    <cfRule type="duplicateValues" dxfId="963" priority="964"/>
+    <cfRule type="duplicateValues" dxfId="962" priority="963"/>
+    <cfRule type="duplicateValues" dxfId="961" priority="962"/>
+    <cfRule type="duplicateValues" dxfId="960" priority="961"/>
+    <cfRule type="duplicateValues" dxfId="959" priority="1024"/>
+    <cfRule type="duplicateValues" dxfId="958" priority="959"/>
+    <cfRule type="duplicateValues" dxfId="957" priority="958"/>
+    <cfRule type="duplicateValues" dxfId="956" priority="957"/>
+    <cfRule type="duplicateValues" dxfId="955" priority="956"/>
+    <cfRule type="duplicateValues" dxfId="954" priority="955"/>
+    <cfRule type="duplicateValues" dxfId="953" priority="954"/>
+    <cfRule type="duplicateValues" dxfId="952" priority="953"/>
+    <cfRule type="duplicateValues" dxfId="951" priority="952"/>
+    <cfRule type="duplicateValues" dxfId="950" priority="951"/>
+    <cfRule type="duplicateValues" dxfId="949" priority="950"/>
+    <cfRule type="duplicateValues" dxfId="948" priority="949"/>
+    <cfRule type="duplicateValues" dxfId="947" priority="948"/>
+    <cfRule type="duplicateValues" dxfId="946" priority="947"/>
+    <cfRule type="duplicateValues" dxfId="945" priority="946"/>
+    <cfRule type="duplicateValues" dxfId="944" priority="945"/>
+    <cfRule type="duplicateValues" dxfId="943" priority="944"/>
+    <cfRule type="duplicateValues" dxfId="942" priority="943"/>
+    <cfRule type="duplicateValues" dxfId="941" priority="942"/>
+    <cfRule type="duplicateValues" dxfId="940" priority="941"/>
+    <cfRule type="duplicateValues" dxfId="939" priority="940"/>
+    <cfRule type="duplicateValues" dxfId="938" priority="939"/>
+    <cfRule type="duplicateValues" dxfId="937" priority="938"/>
+    <cfRule type="duplicateValues" dxfId="936" priority="937"/>
+    <cfRule type="duplicateValues" dxfId="935" priority="936"/>
+    <cfRule type="duplicateValues" dxfId="934" priority="935"/>
+    <cfRule type="duplicateValues" dxfId="933" priority="934"/>
+    <cfRule type="duplicateValues" dxfId="932" priority="933"/>
+    <cfRule type="duplicateValues" dxfId="931" priority="932"/>
+    <cfRule type="duplicateValues" dxfId="930" priority="931"/>
+    <cfRule type="duplicateValues" dxfId="929" priority="930"/>
+    <cfRule type="duplicateValues" dxfId="928" priority="929"/>
+    <cfRule type="duplicateValues" dxfId="927" priority="928"/>
+    <cfRule type="duplicateValues" dxfId="926" priority="927"/>
+    <cfRule type="duplicateValues" dxfId="925" priority="926"/>
+    <cfRule type="duplicateValues" dxfId="924" priority="925"/>
+    <cfRule type="duplicateValues" dxfId="923" priority="924"/>
+    <cfRule type="duplicateValues" dxfId="922" priority="923"/>
+    <cfRule type="duplicateValues" dxfId="921" priority="922"/>
+    <cfRule type="duplicateValues" dxfId="920" priority="921"/>
+    <cfRule type="duplicateValues" dxfId="919" priority="920"/>
+    <cfRule type="duplicateValues" dxfId="918" priority="919"/>
+    <cfRule type="duplicateValues" dxfId="917" priority="918"/>
+    <cfRule type="duplicateValues" dxfId="916" priority="917"/>
+    <cfRule type="duplicateValues" dxfId="915" priority="916"/>
+    <cfRule type="duplicateValues" dxfId="914" priority="915"/>
+    <cfRule type="duplicateValues" dxfId="913" priority="914"/>
+    <cfRule type="duplicateValues" dxfId="912" priority="913"/>
+    <cfRule type="duplicateValues" dxfId="911" priority="912"/>
+    <cfRule type="duplicateValues" dxfId="910" priority="911"/>
+    <cfRule type="duplicateValues" dxfId="909" priority="910"/>
+    <cfRule type="duplicateValues" dxfId="908" priority="909"/>
+    <cfRule type="duplicateValues" dxfId="907" priority="908"/>
+    <cfRule type="duplicateValues" dxfId="906" priority="907"/>
+    <cfRule type="duplicateValues" dxfId="905" priority="906"/>
+    <cfRule type="duplicateValues" dxfId="904" priority="905"/>
+    <cfRule type="duplicateValues" dxfId="903" priority="904"/>
+    <cfRule type="duplicateValues" dxfId="902" priority="903"/>
+    <cfRule type="duplicateValues" dxfId="901" priority="902"/>
+    <cfRule type="duplicateValues" dxfId="900" priority="901"/>
+    <cfRule type="duplicateValues" dxfId="899" priority="900"/>
+    <cfRule type="duplicateValues" dxfId="898" priority="899"/>
+    <cfRule type="duplicateValues" dxfId="897" priority="898"/>
+    <cfRule type="duplicateValues" dxfId="896" priority="897"/>
+    <cfRule type="duplicateValues" dxfId="895" priority="896"/>
+    <cfRule type="duplicateValues" dxfId="894" priority="895"/>
+    <cfRule type="duplicateValues" dxfId="893" priority="894"/>
+    <cfRule type="duplicateValues" dxfId="892" priority="893"/>
+    <cfRule type="duplicateValues" dxfId="891" priority="892"/>
+    <cfRule type="duplicateValues" dxfId="890" priority="891"/>
+    <cfRule type="duplicateValues" dxfId="889" priority="890"/>
+    <cfRule type="duplicateValues" dxfId="888" priority="889"/>
+    <cfRule type="duplicateValues" dxfId="887" priority="888"/>
+    <cfRule type="duplicateValues" dxfId="886" priority="887"/>
+    <cfRule type="duplicateValues" dxfId="885" priority="886"/>
+    <cfRule type="duplicateValues" dxfId="884" priority="885"/>
+    <cfRule type="duplicateValues" dxfId="883" priority="884"/>
+    <cfRule type="duplicateValues" dxfId="882" priority="883"/>
+    <cfRule type="duplicateValues" dxfId="881" priority="882"/>
+    <cfRule type="duplicateValues" dxfId="880" priority="881"/>
+    <cfRule type="duplicateValues" dxfId="879" priority="880"/>
+    <cfRule type="duplicateValues" dxfId="878" priority="879"/>
+    <cfRule type="duplicateValues" dxfId="877" priority="878"/>
+    <cfRule type="duplicateValues" dxfId="876" priority="877"/>
+    <cfRule type="duplicateValues" dxfId="875" priority="876"/>
+    <cfRule type="duplicateValues" dxfId="874" priority="875"/>
+    <cfRule type="duplicateValues" dxfId="873" priority="874"/>
+    <cfRule type="duplicateValues" dxfId="872" priority="873"/>
+    <cfRule type="duplicateValues" dxfId="871" priority="872"/>
+    <cfRule type="duplicateValues" dxfId="870" priority="871"/>
+    <cfRule type="duplicateValues" dxfId="869" priority="870"/>
+    <cfRule type="duplicateValues" dxfId="868" priority="869"/>
+    <cfRule type="duplicateValues" dxfId="867" priority="868"/>
+    <cfRule type="duplicateValues" dxfId="866" priority="867"/>
+    <cfRule type="duplicateValues" dxfId="865" priority="866"/>
+    <cfRule type="duplicateValues" dxfId="864" priority="865"/>
+    <cfRule type="duplicateValues" dxfId="863" priority="864"/>
+    <cfRule type="duplicateValues" dxfId="862" priority="863"/>
+    <cfRule type="duplicateValues" dxfId="861" priority="862"/>
+    <cfRule type="duplicateValues" dxfId="860" priority="861"/>
+    <cfRule type="duplicateValues" dxfId="859" priority="860"/>
+    <cfRule type="duplicateValues" dxfId="858" priority="859"/>
+    <cfRule type="duplicateValues" dxfId="857" priority="858"/>
+    <cfRule type="duplicateValues" dxfId="856" priority="857"/>
+    <cfRule type="duplicateValues" dxfId="855" priority="856"/>
+    <cfRule type="duplicateValues" dxfId="854" priority="855"/>
+    <cfRule type="duplicateValues" dxfId="853" priority="854"/>
+    <cfRule type="duplicateValues" dxfId="852" priority="853"/>
+    <cfRule type="duplicateValues" dxfId="851" priority="852"/>
+    <cfRule type="duplicateValues" dxfId="850" priority="851"/>
+    <cfRule type="duplicateValues" dxfId="849" priority="850"/>
+    <cfRule type="duplicateValues" dxfId="848" priority="849"/>
+    <cfRule type="duplicateValues" dxfId="847" priority="848"/>
+    <cfRule type="duplicateValues" dxfId="846" priority="847"/>
+    <cfRule type="duplicateValues" dxfId="845" priority="846"/>
+    <cfRule type="duplicateValues" dxfId="844" priority="845"/>
+    <cfRule type="duplicateValues" dxfId="843" priority="844"/>
+    <cfRule type="duplicateValues" dxfId="842" priority="843"/>
+    <cfRule type="duplicateValues" dxfId="841" priority="842"/>
+    <cfRule type="duplicateValues" dxfId="840" priority="841"/>
+    <cfRule type="duplicateValues" dxfId="839" priority="840"/>
+    <cfRule type="duplicateValues" dxfId="838" priority="839"/>
+    <cfRule type="duplicateValues" dxfId="837" priority="838"/>
+    <cfRule type="duplicateValues" dxfId="836" priority="837"/>
+    <cfRule type="duplicateValues" dxfId="835" priority="836"/>
+    <cfRule type="duplicateValues" dxfId="834" priority="835"/>
+    <cfRule type="duplicateValues" dxfId="833" priority="834"/>
+    <cfRule type="duplicateValues" dxfId="832" priority="833"/>
+    <cfRule type="duplicateValues" dxfId="831" priority="832"/>
+    <cfRule type="duplicateValues" dxfId="830" priority="831"/>
+    <cfRule type="duplicateValues" dxfId="829" priority="830"/>
+    <cfRule type="duplicateValues" dxfId="828" priority="829"/>
+    <cfRule type="duplicateValues" dxfId="827" priority="828"/>
+    <cfRule type="duplicateValues" dxfId="826" priority="827"/>
+    <cfRule type="duplicateValues" dxfId="825" priority="826"/>
+    <cfRule type="duplicateValues" dxfId="824" priority="825"/>
+    <cfRule type="duplicateValues" dxfId="823" priority="824"/>
+    <cfRule type="duplicateValues" dxfId="822" priority="823"/>
+    <cfRule type="duplicateValues" dxfId="821" priority="822"/>
+    <cfRule type="duplicateValues" dxfId="820" priority="821"/>
+    <cfRule type="duplicateValues" dxfId="819" priority="820"/>
+    <cfRule type="duplicateValues" dxfId="818" priority="819"/>
+    <cfRule type="duplicateValues" dxfId="817" priority="818"/>
+    <cfRule type="duplicateValues" dxfId="816" priority="817"/>
+    <cfRule type="duplicateValues" dxfId="815" priority="816"/>
+    <cfRule type="duplicateValues" dxfId="814" priority="815"/>
+    <cfRule type="duplicateValues" dxfId="813" priority="814"/>
+    <cfRule type="duplicateValues" dxfId="812" priority="813"/>
+    <cfRule type="duplicateValues" dxfId="811" priority="812"/>
+    <cfRule type="duplicateValues" dxfId="810" priority="811"/>
+    <cfRule type="duplicateValues" dxfId="809" priority="810"/>
+    <cfRule type="duplicateValues" dxfId="808" priority="809"/>
+    <cfRule type="duplicateValues" dxfId="807" priority="808"/>
+    <cfRule type="duplicateValues" dxfId="806" priority="807"/>
+    <cfRule type="duplicateValues" dxfId="805" priority="806"/>
+    <cfRule type="duplicateValues" dxfId="804" priority="805"/>
+    <cfRule type="duplicateValues" dxfId="803" priority="804"/>
+    <cfRule type="duplicateValues" dxfId="802" priority="803"/>
+    <cfRule type="duplicateValues" dxfId="801" priority="802"/>
     <cfRule type="duplicateValues" dxfId="800" priority="800"/>
     <cfRule type="duplicateValues" dxfId="799" priority="801"/>
-    <cfRule type="duplicateValues" dxfId="801" priority="802"/>
-    <cfRule type="duplicateValues" dxfId="802" priority="803"/>
-    <cfRule type="duplicateValues" dxfId="803" priority="804"/>
-    <cfRule type="duplicateValues" dxfId="804" priority="805"/>
-    <cfRule type="duplicateValues" dxfId="805" priority="806"/>
-    <cfRule type="duplicateValues" dxfId="806" priority="807"/>
-    <cfRule type="duplicateValues" dxfId="807" priority="808"/>
-    <cfRule type="duplicateValues" dxfId="808" priority="809"/>
-    <cfRule type="duplicateValues" dxfId="809" priority="810"/>
-    <cfRule type="duplicateValues" dxfId="810" priority="811"/>
-    <cfRule type="duplicateValues" dxfId="811" priority="812"/>
-    <cfRule type="duplicateValues" dxfId="812" priority="813"/>
-    <cfRule type="duplicateValues" dxfId="813" priority="814"/>
-    <cfRule type="duplicateValues" dxfId="814" priority="815"/>
-    <cfRule type="duplicateValues" dxfId="815" priority="816"/>
-    <cfRule type="duplicateValues" dxfId="816" priority="817"/>
-    <cfRule type="duplicateValues" dxfId="817" priority="818"/>
-    <cfRule type="duplicateValues" dxfId="818" priority="819"/>
-    <cfRule type="duplicateValues" dxfId="819" priority="820"/>
-    <cfRule type="duplicateValues" dxfId="820" priority="821"/>
-    <cfRule type="duplicateValues" dxfId="821" priority="822"/>
-    <cfRule type="duplicateValues" dxfId="822" priority="823"/>
-    <cfRule type="duplicateValues" dxfId="823" priority="824"/>
-    <cfRule type="duplicateValues" dxfId="824" priority="825"/>
-    <cfRule type="duplicateValues" dxfId="825" priority="826"/>
-    <cfRule type="duplicateValues" dxfId="826" priority="827"/>
-    <cfRule type="duplicateValues" dxfId="827" priority="828"/>
-    <cfRule type="duplicateValues" dxfId="828" priority="829"/>
-    <cfRule type="duplicateValues" dxfId="829" priority="830"/>
-    <cfRule type="duplicateValues" dxfId="830" priority="831"/>
-    <cfRule type="duplicateValues" dxfId="831" priority="832"/>
-    <cfRule type="duplicateValues" dxfId="832" priority="833"/>
-    <cfRule type="duplicateValues" dxfId="833" priority="834"/>
-    <cfRule type="duplicateValues" dxfId="834" priority="835"/>
-    <cfRule type="duplicateValues" dxfId="835" priority="836"/>
-    <cfRule type="duplicateValues" dxfId="836" priority="837"/>
-    <cfRule type="duplicateValues" dxfId="837" priority="838"/>
-    <cfRule type="duplicateValues" dxfId="838" priority="839"/>
-    <cfRule type="duplicateValues" dxfId="839" priority="840"/>
-    <cfRule type="duplicateValues" dxfId="840" priority="841"/>
-    <cfRule type="duplicateValues" dxfId="841" priority="842"/>
-    <cfRule type="duplicateValues" dxfId="842" priority="843"/>
-    <cfRule type="duplicateValues" dxfId="843" priority="844"/>
-    <cfRule type="duplicateValues" dxfId="844" priority="845"/>
-    <cfRule type="duplicateValues" dxfId="845" priority="846"/>
-    <cfRule type="duplicateValues" dxfId="846" priority="847"/>
-    <cfRule type="duplicateValues" dxfId="847" priority="848"/>
-    <cfRule type="duplicateValues" dxfId="848" priority="849"/>
-    <cfRule type="duplicateValues" dxfId="849" priority="850"/>
-    <cfRule type="duplicateValues" dxfId="850" priority="851"/>
-    <cfRule type="duplicateValues" dxfId="851" priority="852"/>
-    <cfRule type="duplicateValues" dxfId="852" priority="853"/>
-    <cfRule type="duplicateValues" dxfId="853" priority="854"/>
-    <cfRule type="duplicateValues" dxfId="854" priority="855"/>
-    <cfRule type="duplicateValues" dxfId="855" priority="856"/>
-    <cfRule type="duplicateValues" dxfId="856" priority="857"/>
-    <cfRule type="duplicateValues" dxfId="857" priority="858"/>
-    <cfRule type="duplicateValues" dxfId="858" priority="859"/>
-    <cfRule type="duplicateValues" dxfId="859" priority="860"/>
-    <cfRule type="duplicateValues" dxfId="860" priority="861"/>
-    <cfRule type="duplicateValues" dxfId="861" priority="862"/>
-    <cfRule type="duplicateValues" dxfId="862" priority="863"/>
-    <cfRule type="duplicateValues" dxfId="863" priority="864"/>
-    <cfRule type="duplicateValues" dxfId="864" priority="865"/>
-    <cfRule type="duplicateValues" dxfId="865" priority="866"/>
-    <cfRule type="duplicateValues" dxfId="866" priority="867"/>
-    <cfRule type="duplicateValues" dxfId="867" priority="868"/>
-    <cfRule type="duplicateValues" dxfId="868" priority="869"/>
-    <cfRule type="duplicateValues" dxfId="869" priority="870"/>
-    <cfRule type="duplicateValues" dxfId="870" priority="871"/>
-    <cfRule type="duplicateValues" dxfId="871" priority="872"/>
-    <cfRule type="duplicateValues" dxfId="872" priority="873"/>
-    <cfRule type="duplicateValues" dxfId="873" priority="874"/>
-    <cfRule type="duplicateValues" dxfId="874" priority="875"/>
-    <cfRule type="duplicateValues" dxfId="875" priority="876"/>
-    <cfRule type="duplicateValues" dxfId="876" priority="877"/>
-    <cfRule type="duplicateValues" dxfId="877" priority="878"/>
-    <cfRule type="duplicateValues" dxfId="878" priority="879"/>
-    <cfRule type="duplicateValues" dxfId="879" priority="880"/>
-    <cfRule type="duplicateValues" dxfId="880" priority="881"/>
-    <cfRule type="duplicateValues" dxfId="881" priority="882"/>
-    <cfRule type="duplicateValues" dxfId="882" priority="883"/>
-    <cfRule type="duplicateValues" dxfId="883" priority="884"/>
-    <cfRule type="duplicateValues" dxfId="884" priority="885"/>
-    <cfRule type="duplicateValues" dxfId="885" priority="886"/>
-    <cfRule type="duplicateValues" dxfId="886" priority="887"/>
-    <cfRule type="duplicateValues" dxfId="887" priority="888"/>
-    <cfRule type="duplicateValues" dxfId="888" priority="889"/>
-    <cfRule type="duplicateValues" dxfId="889" priority="890"/>
-    <cfRule type="duplicateValues" dxfId="890" priority="891"/>
-    <cfRule type="duplicateValues" dxfId="891" priority="892"/>
-    <cfRule type="duplicateValues" dxfId="892" priority="893"/>
-    <cfRule type="duplicateValues" dxfId="893" priority="894"/>
-    <cfRule type="duplicateValues" dxfId="894" priority="895"/>
-    <cfRule type="duplicateValues" dxfId="895" priority="896"/>
-    <cfRule type="duplicateValues" dxfId="896" priority="897"/>
-    <cfRule type="duplicateValues" dxfId="897" priority="898"/>
-    <cfRule type="duplicateValues" dxfId="898" priority="899"/>
-    <cfRule type="duplicateValues" dxfId="899" priority="900"/>
-    <cfRule type="duplicateValues" dxfId="900" priority="901"/>
-    <cfRule type="duplicateValues" dxfId="901" priority="902"/>
-    <cfRule type="duplicateValues" dxfId="902" priority="903"/>
-    <cfRule type="duplicateValues" dxfId="903" priority="904"/>
-    <cfRule type="duplicateValues" dxfId="904" priority="905"/>
-    <cfRule type="duplicateValues" dxfId="905" priority="906"/>
-    <cfRule type="duplicateValues" dxfId="906" priority="907"/>
-    <cfRule type="duplicateValues" dxfId="907" priority="908"/>
-    <cfRule type="duplicateValues" dxfId="908" priority="909"/>
-    <cfRule type="duplicateValues" dxfId="909" priority="910"/>
-    <cfRule type="duplicateValues" dxfId="910" priority="911"/>
-    <cfRule type="duplicateValues" dxfId="911" priority="912"/>
-    <cfRule type="duplicateValues" dxfId="912" priority="913"/>
-    <cfRule type="duplicateValues" dxfId="913" priority="914"/>
-    <cfRule type="duplicateValues" dxfId="914" priority="915"/>
-    <cfRule type="duplicateValues" dxfId="915" priority="916"/>
-    <cfRule type="duplicateValues" dxfId="916" priority="917"/>
-    <cfRule type="duplicateValues" dxfId="917" priority="918"/>
-    <cfRule type="duplicateValues" dxfId="918" priority="919"/>
-    <cfRule type="duplicateValues" dxfId="919" priority="920"/>
-    <cfRule type="duplicateValues" dxfId="920" priority="921"/>
-    <cfRule type="duplicateValues" dxfId="921" priority="922"/>
-    <cfRule type="duplicateValues" dxfId="922" priority="923"/>
-    <cfRule type="duplicateValues" dxfId="923" priority="924"/>
-    <cfRule type="duplicateValues" dxfId="924" priority="925"/>
-    <cfRule type="duplicateValues" dxfId="925" priority="926"/>
-    <cfRule type="duplicateValues" dxfId="926" priority="927"/>
-    <cfRule type="duplicateValues" dxfId="927" priority="928"/>
-    <cfRule type="duplicateValues" dxfId="928" priority="929"/>
-    <cfRule type="duplicateValues" dxfId="929" priority="930"/>
-    <cfRule type="duplicateValues" dxfId="930" priority="931"/>
-    <cfRule type="duplicateValues" dxfId="931" priority="932"/>
-    <cfRule type="duplicateValues" dxfId="932" priority="933"/>
-    <cfRule type="duplicateValues" dxfId="933" priority="934"/>
-    <cfRule type="duplicateValues" dxfId="934" priority="935"/>
-    <cfRule type="duplicateValues" dxfId="935" priority="936"/>
-    <cfRule type="duplicateValues" dxfId="936" priority="937"/>
-    <cfRule type="duplicateValues" dxfId="937" priority="938"/>
-    <cfRule type="duplicateValues" dxfId="938" priority="939"/>
-    <cfRule type="duplicateValues" dxfId="939" priority="940"/>
-    <cfRule type="duplicateValues" dxfId="940" priority="941"/>
-    <cfRule type="duplicateValues" dxfId="941" priority="942"/>
-    <cfRule type="duplicateValues" dxfId="942" priority="943"/>
-    <cfRule type="duplicateValues" dxfId="943" priority="944"/>
-    <cfRule type="duplicateValues" dxfId="944" priority="945"/>
-    <cfRule type="duplicateValues" dxfId="945" priority="946"/>
-    <cfRule type="duplicateValues" dxfId="946" priority="947"/>
-    <cfRule type="duplicateValues" dxfId="947" priority="948"/>
-    <cfRule type="duplicateValues" dxfId="948" priority="949"/>
-    <cfRule type="duplicateValues" dxfId="949" priority="950"/>
-    <cfRule type="duplicateValues" dxfId="950" priority="951"/>
-    <cfRule type="duplicateValues" dxfId="951" priority="952"/>
-    <cfRule type="duplicateValues" dxfId="952" priority="953"/>
-    <cfRule type="duplicateValues" dxfId="953" priority="954"/>
-    <cfRule type="duplicateValues" dxfId="954" priority="955"/>
-    <cfRule type="duplicateValues" dxfId="955" priority="956"/>
-    <cfRule type="duplicateValues" dxfId="956" priority="957"/>
-    <cfRule type="duplicateValues" dxfId="957" priority="958"/>
-    <cfRule type="duplicateValues" dxfId="958" priority="959"/>
-    <cfRule type="duplicateValues" dxfId="1023" priority="960"/>
-    <cfRule type="duplicateValues" dxfId="960" priority="961"/>
-    <cfRule type="duplicateValues" dxfId="961" priority="962"/>
-    <cfRule type="duplicateValues" dxfId="962" priority="963"/>
-    <cfRule type="duplicateValues" dxfId="963" priority="964"/>
-    <cfRule type="duplicateValues" dxfId="964" priority="965"/>
-    <cfRule type="duplicateValues" dxfId="965" priority="966"/>
-    <cfRule type="duplicateValues" dxfId="966" priority="967"/>
-    <cfRule type="duplicateValues" dxfId="967" priority="968"/>
-    <cfRule type="duplicateValues" dxfId="968" priority="969"/>
-    <cfRule type="duplicateValues" dxfId="969" priority="970"/>
-    <cfRule type="duplicateValues" dxfId="970" priority="971"/>
-    <cfRule type="duplicateValues" dxfId="971" priority="972"/>
-    <cfRule type="duplicateValues" dxfId="972" priority="973"/>
-    <cfRule type="duplicateValues" dxfId="973" priority="974"/>
-    <cfRule type="duplicateValues" dxfId="974" priority="975"/>
-    <cfRule type="duplicateValues" dxfId="975" priority="976"/>
-    <cfRule type="duplicateValues" dxfId="976" priority="977"/>
-    <cfRule type="duplicateValues" dxfId="977" priority="978"/>
-    <cfRule type="duplicateValues" dxfId="978" priority="979"/>
-    <cfRule type="duplicateValues" dxfId="979" priority="980"/>
-    <cfRule type="duplicateValues" dxfId="980" priority="981"/>
-    <cfRule type="duplicateValues" dxfId="981" priority="982"/>
-    <cfRule type="duplicateValues" dxfId="982" priority="983"/>
-    <cfRule type="duplicateValues" dxfId="983" priority="984"/>
-    <cfRule type="duplicateValues" dxfId="984" priority="985"/>
-    <cfRule type="duplicateValues" dxfId="985" priority="986"/>
-    <cfRule type="duplicateValues" dxfId="986" priority="987"/>
-    <cfRule type="duplicateValues" dxfId="987" priority="988"/>
-    <cfRule type="duplicateValues" dxfId="988" priority="989"/>
-    <cfRule type="duplicateValues" dxfId="989" priority="990"/>
-    <cfRule type="duplicateValues" dxfId="990" priority="991"/>
-    <cfRule type="duplicateValues" dxfId="991" priority="992"/>
-    <cfRule type="duplicateValues" dxfId="992" priority="993"/>
-    <cfRule type="duplicateValues" dxfId="993" priority="994"/>
-    <cfRule type="duplicateValues" dxfId="994" priority="995"/>
-    <cfRule type="duplicateValues" dxfId="995" priority="996"/>
-    <cfRule type="duplicateValues" dxfId="996" priority="997"/>
-    <cfRule type="duplicateValues" dxfId="997" priority="998"/>
-    <cfRule type="duplicateValues" dxfId="998" priority="999"/>
-    <cfRule type="duplicateValues" dxfId="999" priority="1000"/>
-    <cfRule type="duplicateValues" dxfId="1000" priority="1001"/>
-    <cfRule type="duplicateValues" dxfId="1001" priority="1002"/>
-    <cfRule type="duplicateValues" dxfId="1002" priority="1003"/>
-    <cfRule type="duplicateValues" dxfId="1003" priority="1004"/>
-    <cfRule type="duplicateValues" dxfId="1004" priority="1005"/>
-    <cfRule type="duplicateValues" dxfId="1005" priority="1006"/>
-    <cfRule type="duplicateValues" dxfId="1006" priority="1007"/>
-    <cfRule type="duplicateValues" dxfId="1007" priority="1008"/>
-    <cfRule type="duplicateValues" dxfId="1008" priority="1009"/>
-    <cfRule type="duplicateValues" dxfId="1009" priority="1010"/>
-    <cfRule type="duplicateValues" dxfId="1010" priority="1011"/>
-    <cfRule type="duplicateValues" dxfId="1011" priority="1012"/>
-    <cfRule type="duplicateValues" dxfId="1012" priority="1013"/>
-    <cfRule type="duplicateValues" dxfId="1013" priority="1014"/>
-    <cfRule type="duplicateValues" dxfId="1014" priority="1015"/>
-    <cfRule type="duplicateValues" dxfId="1015" priority="1016"/>
-    <cfRule type="duplicateValues" dxfId="1016" priority="1017"/>
-    <cfRule type="duplicateValues" dxfId="1017" priority="1018"/>
-    <cfRule type="duplicateValues" dxfId="1018" priority="1019"/>
-    <cfRule type="duplicateValues" dxfId="1019" priority="1020"/>
-    <cfRule type="duplicateValues" dxfId="1020" priority="1021"/>
-    <cfRule type="duplicateValues" dxfId="1021" priority="1022"/>
-    <cfRule type="duplicateValues" dxfId="1022" priority="1023"/>
-    <cfRule type="duplicateValues" dxfId="959" priority="1024"/>
+    <cfRule type="duplicateValues" dxfId="798" priority="799"/>
+    <cfRule type="duplicateValues" dxfId="797" priority="798"/>
+    <cfRule type="duplicateValues" dxfId="796" priority="797"/>
+    <cfRule type="duplicateValues" dxfId="795" priority="796"/>
+    <cfRule type="duplicateValues" dxfId="794" priority="795"/>
+    <cfRule type="duplicateValues" dxfId="793" priority="794"/>
+    <cfRule type="duplicateValues" dxfId="792" priority="793"/>
+    <cfRule type="duplicateValues" dxfId="791" priority="792"/>
+    <cfRule type="duplicateValues" dxfId="790" priority="791"/>
+    <cfRule type="duplicateValues" dxfId="789" priority="790"/>
+    <cfRule type="duplicateValues" dxfId="788" priority="789"/>
+    <cfRule type="duplicateValues" dxfId="787" priority="788"/>
+    <cfRule type="duplicateValues" dxfId="786" priority="787"/>
+    <cfRule type="duplicateValues" dxfId="785" priority="786"/>
+    <cfRule type="duplicateValues" dxfId="784" priority="785"/>
+    <cfRule type="duplicateValues" dxfId="783" priority="784"/>
+    <cfRule type="duplicateValues" dxfId="782" priority="783"/>
+    <cfRule type="duplicateValues" dxfId="781" priority="782"/>
+    <cfRule type="duplicateValues" dxfId="780" priority="781"/>
+    <cfRule type="duplicateValues" dxfId="779" priority="780"/>
+    <cfRule type="duplicateValues" dxfId="778" priority="779"/>
+    <cfRule type="duplicateValues" dxfId="777" priority="778"/>
+    <cfRule type="duplicateValues" dxfId="776" priority="777"/>
+    <cfRule type="duplicateValues" dxfId="775" priority="776"/>
+    <cfRule type="duplicateValues" dxfId="774" priority="775"/>
+    <cfRule type="duplicateValues" dxfId="773" priority="774"/>
+    <cfRule type="duplicateValues" dxfId="772" priority="773"/>
+    <cfRule type="duplicateValues" dxfId="771" priority="772"/>
+    <cfRule type="duplicateValues" dxfId="770" priority="771"/>
+    <cfRule type="duplicateValues" dxfId="769" priority="770"/>
+    <cfRule type="duplicateValues" dxfId="768" priority="769"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:B207">
     <cfRule type="duplicateValues" dxfId="767" priority="513"/>
@@ -25293,518 +25291,518 @@
     <cfRule type="duplicateValues" dxfId="512" priority="768"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B207">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="91"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="92"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="93"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="95"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="96"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="97"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="98"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="99"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="100"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="101"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="102" priority="103"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="104"/>
-    <cfRule type="duplicateValues" dxfId="104" priority="105"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="106"/>
-    <cfRule type="duplicateValues" dxfId="106" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="107" priority="108"/>
-    <cfRule type="duplicateValues" dxfId="108" priority="109"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="110"/>
-    <cfRule type="duplicateValues" dxfId="110" priority="111"/>
-    <cfRule type="duplicateValues" dxfId="111" priority="112"/>
-    <cfRule type="duplicateValues" dxfId="112" priority="113"/>
-    <cfRule type="duplicateValues" dxfId="113" priority="114"/>
-    <cfRule type="duplicateValues" dxfId="114" priority="115"/>
-    <cfRule type="duplicateValues" dxfId="115" priority="116"/>
-    <cfRule type="duplicateValues" dxfId="116" priority="117"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="118"/>
-    <cfRule type="duplicateValues" dxfId="118" priority="119"/>
-    <cfRule type="duplicateValues" dxfId="119" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="120" priority="121"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="122"/>
-    <cfRule type="duplicateValues" dxfId="122" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="123" priority="124"/>
-    <cfRule type="duplicateValues" dxfId="124" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="125" priority="126"/>
-    <cfRule type="duplicateValues" dxfId="126" priority="127"/>
-    <cfRule type="duplicateValues" dxfId="127" priority="128"/>
-    <cfRule type="duplicateValues" dxfId="128" priority="129"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="130"/>
-    <cfRule type="duplicateValues" dxfId="130" priority="131"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="132"/>
-    <cfRule type="duplicateValues" dxfId="132" priority="133"/>
-    <cfRule type="duplicateValues" dxfId="133" priority="134"/>
-    <cfRule type="duplicateValues" dxfId="134" priority="135"/>
-    <cfRule type="duplicateValues" dxfId="135" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="136" priority="137"/>
-    <cfRule type="duplicateValues" dxfId="137" priority="138"/>
-    <cfRule type="duplicateValues" dxfId="138" priority="139"/>
-    <cfRule type="duplicateValues" dxfId="139" priority="140"/>
-    <cfRule type="duplicateValues" dxfId="140" priority="141"/>
-    <cfRule type="duplicateValues" dxfId="141" priority="142"/>
-    <cfRule type="duplicateValues" dxfId="142" priority="143"/>
-    <cfRule type="duplicateValues" dxfId="143" priority="144"/>
-    <cfRule type="duplicateValues" dxfId="144" priority="145"/>
-    <cfRule type="duplicateValues" dxfId="145" priority="146"/>
-    <cfRule type="duplicateValues" dxfId="146" priority="147"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="148"/>
-    <cfRule type="duplicateValues" dxfId="148" priority="149"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="150"/>
-    <cfRule type="duplicateValues" dxfId="150" priority="151"/>
-    <cfRule type="duplicateValues" dxfId="151" priority="152"/>
-    <cfRule type="duplicateValues" dxfId="152" priority="153"/>
-    <cfRule type="duplicateValues" dxfId="153" priority="154"/>
-    <cfRule type="duplicateValues" dxfId="154" priority="155"/>
-    <cfRule type="duplicateValues" dxfId="155" priority="156"/>
-    <cfRule type="duplicateValues" dxfId="156" priority="157"/>
-    <cfRule type="duplicateValues" dxfId="157" priority="158"/>
-    <cfRule type="duplicateValues" dxfId="158" priority="159"/>
-    <cfRule type="duplicateValues" dxfId="159" priority="160"/>
-    <cfRule type="duplicateValues" dxfId="160" priority="161"/>
-    <cfRule type="duplicateValues" dxfId="161" priority="162"/>
-    <cfRule type="duplicateValues" dxfId="162" priority="163"/>
-    <cfRule type="duplicateValues" dxfId="163" priority="164"/>
-    <cfRule type="duplicateValues" dxfId="164" priority="165"/>
-    <cfRule type="duplicateValues" dxfId="165" priority="166"/>
-    <cfRule type="duplicateValues" dxfId="166" priority="167"/>
-    <cfRule type="duplicateValues" dxfId="167" priority="168"/>
-    <cfRule type="duplicateValues" dxfId="168" priority="169"/>
-    <cfRule type="duplicateValues" dxfId="169" priority="170"/>
-    <cfRule type="duplicateValues" dxfId="170" priority="171"/>
-    <cfRule type="duplicateValues" dxfId="171" priority="172"/>
-    <cfRule type="duplicateValues" dxfId="172" priority="173"/>
-    <cfRule type="duplicateValues" dxfId="173" priority="174"/>
-    <cfRule type="duplicateValues" dxfId="174" priority="175"/>
-    <cfRule type="duplicateValues" dxfId="175" priority="176"/>
-    <cfRule type="duplicateValues" dxfId="176" priority="177"/>
-    <cfRule type="duplicateValues" dxfId="177" priority="178"/>
-    <cfRule type="duplicateValues" dxfId="178" priority="179"/>
-    <cfRule type="duplicateValues" dxfId="179" priority="180"/>
-    <cfRule type="duplicateValues" dxfId="180" priority="181"/>
-    <cfRule type="duplicateValues" dxfId="181" priority="182"/>
-    <cfRule type="duplicateValues" dxfId="182" priority="183"/>
-    <cfRule type="duplicateValues" dxfId="183" priority="184"/>
-    <cfRule type="duplicateValues" dxfId="184" priority="185"/>
-    <cfRule type="duplicateValues" dxfId="185" priority="186"/>
-    <cfRule type="duplicateValues" dxfId="186" priority="187"/>
-    <cfRule type="duplicateValues" dxfId="187" priority="188"/>
-    <cfRule type="duplicateValues" dxfId="188" priority="189"/>
-    <cfRule type="duplicateValues" dxfId="189" priority="190"/>
-    <cfRule type="duplicateValues" dxfId="190" priority="191"/>
-    <cfRule type="duplicateValues" dxfId="191" priority="192"/>
-    <cfRule type="duplicateValues" dxfId="192" priority="193"/>
-    <cfRule type="duplicateValues" dxfId="193" priority="194"/>
-    <cfRule type="duplicateValues" dxfId="194" priority="195"/>
-    <cfRule type="duplicateValues" dxfId="195" priority="196"/>
-    <cfRule type="duplicateValues" dxfId="196" priority="197"/>
-    <cfRule type="duplicateValues" dxfId="197" priority="198"/>
-    <cfRule type="duplicateValues" dxfId="198" priority="199"/>
-    <cfRule type="duplicateValues" dxfId="199" priority="200"/>
-    <cfRule type="duplicateValues" dxfId="200" priority="201"/>
-    <cfRule type="duplicateValues" dxfId="201" priority="202"/>
-    <cfRule type="duplicateValues" dxfId="202" priority="203"/>
-    <cfRule type="duplicateValues" dxfId="203" priority="204"/>
-    <cfRule type="duplicateValues" dxfId="204" priority="205"/>
-    <cfRule type="duplicateValues" dxfId="205" priority="206"/>
-    <cfRule type="duplicateValues" dxfId="206" priority="207"/>
-    <cfRule type="duplicateValues" dxfId="207" priority="208"/>
-    <cfRule type="duplicateValues" dxfId="208" priority="209"/>
-    <cfRule type="duplicateValues" dxfId="209" priority="210"/>
-    <cfRule type="duplicateValues" dxfId="210" priority="211"/>
-    <cfRule type="duplicateValues" dxfId="211" priority="212"/>
-    <cfRule type="duplicateValues" dxfId="212" priority="213"/>
-    <cfRule type="duplicateValues" dxfId="213" priority="214"/>
-    <cfRule type="duplicateValues" dxfId="214" priority="215"/>
-    <cfRule type="duplicateValues" dxfId="215" priority="216"/>
-    <cfRule type="duplicateValues" dxfId="216" priority="217"/>
-    <cfRule type="duplicateValues" dxfId="217" priority="218"/>
-    <cfRule type="duplicateValues" dxfId="218" priority="219"/>
-    <cfRule type="duplicateValues" dxfId="219" priority="220"/>
-    <cfRule type="duplicateValues" dxfId="220" priority="221"/>
-    <cfRule type="duplicateValues" dxfId="221" priority="222"/>
-    <cfRule type="duplicateValues" dxfId="222" priority="223"/>
-    <cfRule type="duplicateValues" dxfId="223" priority="224"/>
-    <cfRule type="duplicateValues" dxfId="224" priority="225"/>
-    <cfRule type="duplicateValues" dxfId="225" priority="226"/>
-    <cfRule type="duplicateValues" dxfId="226" priority="227"/>
-    <cfRule type="duplicateValues" dxfId="227" priority="228"/>
-    <cfRule type="duplicateValues" dxfId="228" priority="229"/>
-    <cfRule type="duplicateValues" dxfId="229" priority="230"/>
-    <cfRule type="duplicateValues" dxfId="230" priority="231"/>
-    <cfRule type="duplicateValues" dxfId="231" priority="232"/>
-    <cfRule type="duplicateValues" dxfId="232" priority="233"/>
-    <cfRule type="duplicateValues" dxfId="233" priority="234"/>
-    <cfRule type="duplicateValues" dxfId="234" priority="235"/>
-    <cfRule type="duplicateValues" dxfId="235" priority="236"/>
-    <cfRule type="duplicateValues" dxfId="236" priority="237"/>
-    <cfRule type="duplicateValues" dxfId="237" priority="238"/>
-    <cfRule type="duplicateValues" dxfId="238" priority="239"/>
-    <cfRule type="duplicateValues" dxfId="239" priority="240"/>
-    <cfRule type="duplicateValues" dxfId="240" priority="241"/>
-    <cfRule type="duplicateValues" dxfId="241" priority="242"/>
-    <cfRule type="duplicateValues" dxfId="242" priority="243"/>
-    <cfRule type="duplicateValues" dxfId="243" priority="244"/>
-    <cfRule type="duplicateValues" dxfId="244" priority="245"/>
-    <cfRule type="duplicateValues" dxfId="245" priority="246"/>
-    <cfRule type="duplicateValues" dxfId="246" priority="247"/>
-    <cfRule type="duplicateValues" dxfId="247" priority="248"/>
-    <cfRule type="duplicateValues" dxfId="248" priority="249"/>
-    <cfRule type="duplicateValues" dxfId="249" priority="250"/>
-    <cfRule type="duplicateValues" dxfId="250" priority="251"/>
-    <cfRule type="duplicateValues" dxfId="251" priority="252"/>
-    <cfRule type="duplicateValues" dxfId="252" priority="253"/>
-    <cfRule type="duplicateValues" dxfId="253" priority="254"/>
-    <cfRule type="duplicateValues" dxfId="254" priority="255"/>
-    <cfRule type="duplicateValues" dxfId="255" priority="256"/>
-    <cfRule type="duplicateValues" dxfId="256" priority="257"/>
-    <cfRule type="duplicateValues" dxfId="257" priority="258"/>
-    <cfRule type="duplicateValues" dxfId="258" priority="259"/>
-    <cfRule type="duplicateValues" dxfId="259" priority="260"/>
-    <cfRule type="duplicateValues" dxfId="260" priority="261"/>
-    <cfRule type="duplicateValues" dxfId="261" priority="262"/>
-    <cfRule type="duplicateValues" dxfId="262" priority="263"/>
-    <cfRule type="duplicateValues" dxfId="263" priority="264"/>
-    <cfRule type="duplicateValues" dxfId="264" priority="265"/>
-    <cfRule type="duplicateValues" dxfId="265" priority="266"/>
-    <cfRule type="duplicateValues" dxfId="266" priority="267"/>
-    <cfRule type="duplicateValues" dxfId="267" priority="268"/>
-    <cfRule type="duplicateValues" dxfId="268" priority="269"/>
-    <cfRule type="duplicateValues" dxfId="269" priority="270"/>
-    <cfRule type="duplicateValues" dxfId="270" priority="271"/>
-    <cfRule type="duplicateValues" dxfId="271" priority="272"/>
-    <cfRule type="duplicateValues" dxfId="272" priority="273"/>
-    <cfRule type="duplicateValues" dxfId="273" priority="274"/>
-    <cfRule type="duplicateValues" dxfId="274" priority="275"/>
-    <cfRule type="duplicateValues" dxfId="275" priority="276"/>
-    <cfRule type="duplicateValues" dxfId="276" priority="277"/>
-    <cfRule type="duplicateValues" dxfId="277" priority="278"/>
-    <cfRule type="duplicateValues" dxfId="278" priority="279"/>
-    <cfRule type="duplicateValues" dxfId="279" priority="280"/>
-    <cfRule type="duplicateValues" dxfId="280" priority="281"/>
-    <cfRule type="duplicateValues" dxfId="281" priority="282"/>
-    <cfRule type="duplicateValues" dxfId="282" priority="283"/>
-    <cfRule type="duplicateValues" dxfId="283" priority="284"/>
-    <cfRule type="duplicateValues" dxfId="284" priority="285"/>
-    <cfRule type="duplicateValues" dxfId="285" priority="286"/>
-    <cfRule type="duplicateValues" dxfId="286" priority="287"/>
-    <cfRule type="duplicateValues" dxfId="287" priority="288"/>
-    <cfRule type="duplicateValues" dxfId="288" priority="289"/>
-    <cfRule type="duplicateValues" dxfId="289" priority="290"/>
-    <cfRule type="duplicateValues" dxfId="290" priority="291"/>
-    <cfRule type="duplicateValues" dxfId="291" priority="292"/>
-    <cfRule type="duplicateValues" dxfId="292" priority="293"/>
-    <cfRule type="duplicateValues" dxfId="293" priority="294"/>
-    <cfRule type="duplicateValues" dxfId="294" priority="295"/>
-    <cfRule type="duplicateValues" dxfId="295" priority="296"/>
-    <cfRule type="duplicateValues" dxfId="296" priority="297"/>
-    <cfRule type="duplicateValues" dxfId="297" priority="298"/>
-    <cfRule type="duplicateValues" dxfId="298" priority="299"/>
-    <cfRule type="duplicateValues" dxfId="299" priority="300"/>
-    <cfRule type="duplicateValues" dxfId="300" priority="301"/>
-    <cfRule type="duplicateValues" dxfId="301" priority="302"/>
-    <cfRule type="duplicateValues" dxfId="302" priority="303"/>
-    <cfRule type="duplicateValues" dxfId="303" priority="304"/>
-    <cfRule type="duplicateValues" dxfId="304" priority="305"/>
-    <cfRule type="duplicateValues" dxfId="305" priority="306"/>
-    <cfRule type="duplicateValues" dxfId="306" priority="307"/>
-    <cfRule type="duplicateValues" dxfId="307" priority="308"/>
-    <cfRule type="duplicateValues" dxfId="308" priority="309"/>
-    <cfRule type="duplicateValues" dxfId="309" priority="310"/>
-    <cfRule type="duplicateValues" dxfId="310" priority="311"/>
-    <cfRule type="duplicateValues" dxfId="311" priority="312"/>
-    <cfRule type="duplicateValues" dxfId="312" priority="313"/>
-    <cfRule type="duplicateValues" dxfId="313" priority="314"/>
-    <cfRule type="duplicateValues" dxfId="314" priority="315"/>
-    <cfRule type="duplicateValues" dxfId="315" priority="316"/>
-    <cfRule type="duplicateValues" dxfId="316" priority="317"/>
-    <cfRule type="duplicateValues" dxfId="317" priority="318"/>
-    <cfRule type="duplicateValues" dxfId="318" priority="319"/>
-    <cfRule type="duplicateValues" dxfId="319" priority="320"/>
-    <cfRule type="duplicateValues" dxfId="320" priority="321"/>
-    <cfRule type="duplicateValues" dxfId="321" priority="322"/>
-    <cfRule type="duplicateValues" dxfId="322" priority="323"/>
-    <cfRule type="duplicateValues" dxfId="323" priority="324"/>
-    <cfRule type="duplicateValues" dxfId="324" priority="325"/>
-    <cfRule type="duplicateValues" dxfId="325" priority="326"/>
-    <cfRule type="duplicateValues" dxfId="326" priority="327"/>
-    <cfRule type="duplicateValues" dxfId="327" priority="328"/>
-    <cfRule type="duplicateValues" dxfId="328" priority="329"/>
-    <cfRule type="duplicateValues" dxfId="329" priority="330"/>
-    <cfRule type="duplicateValues" dxfId="330" priority="331"/>
-    <cfRule type="duplicateValues" dxfId="331" priority="332"/>
-    <cfRule type="duplicateValues" dxfId="332" priority="333"/>
-    <cfRule type="duplicateValues" dxfId="333" priority="334"/>
-    <cfRule type="duplicateValues" dxfId="334" priority="335"/>
-    <cfRule type="duplicateValues" dxfId="335" priority="336"/>
-    <cfRule type="duplicateValues" dxfId="336" priority="337"/>
-    <cfRule type="duplicateValues" dxfId="337" priority="338"/>
-    <cfRule type="duplicateValues" dxfId="338" priority="339"/>
-    <cfRule type="duplicateValues" dxfId="339" priority="340"/>
-    <cfRule type="duplicateValues" dxfId="340" priority="341"/>
-    <cfRule type="duplicateValues" dxfId="341" priority="342"/>
-    <cfRule type="duplicateValues" dxfId="342" priority="343"/>
-    <cfRule type="duplicateValues" dxfId="343" priority="344"/>
-    <cfRule type="duplicateValues" dxfId="344" priority="345"/>
-    <cfRule type="duplicateValues" dxfId="345" priority="346"/>
-    <cfRule type="duplicateValues" dxfId="346" priority="347"/>
-    <cfRule type="duplicateValues" dxfId="347" priority="348"/>
-    <cfRule type="duplicateValues" dxfId="348" priority="349"/>
-    <cfRule type="duplicateValues" dxfId="349" priority="350"/>
-    <cfRule type="duplicateValues" dxfId="350" priority="351"/>
-    <cfRule type="duplicateValues" dxfId="351" priority="352"/>
-    <cfRule type="duplicateValues" dxfId="352" priority="353"/>
-    <cfRule type="duplicateValues" dxfId="353" priority="354"/>
-    <cfRule type="duplicateValues" dxfId="354" priority="355"/>
-    <cfRule type="duplicateValues" dxfId="355" priority="356"/>
-    <cfRule type="duplicateValues" dxfId="356" priority="357"/>
-    <cfRule type="duplicateValues" dxfId="357" priority="358"/>
-    <cfRule type="duplicateValues" dxfId="358" priority="359"/>
-    <cfRule type="duplicateValues" dxfId="359" priority="360"/>
-    <cfRule type="duplicateValues" dxfId="360" priority="361"/>
-    <cfRule type="duplicateValues" dxfId="361" priority="362"/>
-    <cfRule type="duplicateValues" dxfId="362" priority="363"/>
-    <cfRule type="duplicateValues" dxfId="363" priority="364"/>
-    <cfRule type="duplicateValues" dxfId="364" priority="365"/>
-    <cfRule type="duplicateValues" dxfId="365" priority="366"/>
-    <cfRule type="duplicateValues" dxfId="366" priority="367"/>
-    <cfRule type="duplicateValues" dxfId="367" priority="368"/>
-    <cfRule type="duplicateValues" dxfId="368" priority="369"/>
-    <cfRule type="duplicateValues" dxfId="369" priority="370"/>
-    <cfRule type="duplicateValues" dxfId="370" priority="371"/>
-    <cfRule type="duplicateValues" dxfId="371" priority="372"/>
-    <cfRule type="duplicateValues" dxfId="372" priority="373"/>
-    <cfRule type="duplicateValues" dxfId="373" priority="374"/>
-    <cfRule type="duplicateValues" dxfId="374" priority="375"/>
-    <cfRule type="duplicateValues" dxfId="375" priority="376"/>
-    <cfRule type="duplicateValues" dxfId="376" priority="377"/>
-    <cfRule type="duplicateValues" dxfId="377" priority="378"/>
-    <cfRule type="duplicateValues" dxfId="378" priority="379"/>
-    <cfRule type="duplicateValues" dxfId="379" priority="380"/>
-    <cfRule type="duplicateValues" dxfId="380" priority="381"/>
-    <cfRule type="duplicateValues" dxfId="381" priority="382"/>
-    <cfRule type="duplicateValues" dxfId="382" priority="383"/>
-    <cfRule type="duplicateValues" dxfId="383" priority="384"/>
-    <cfRule type="duplicateValues" dxfId="384" priority="385"/>
-    <cfRule type="duplicateValues" dxfId="385" priority="386"/>
-    <cfRule type="duplicateValues" dxfId="386" priority="387"/>
-    <cfRule type="duplicateValues" dxfId="387" priority="388"/>
-    <cfRule type="duplicateValues" dxfId="388" priority="389"/>
-    <cfRule type="duplicateValues" dxfId="389" priority="390"/>
-    <cfRule type="duplicateValues" dxfId="390" priority="391"/>
-    <cfRule type="duplicateValues" dxfId="391" priority="392"/>
-    <cfRule type="duplicateValues" dxfId="392" priority="393"/>
-    <cfRule type="duplicateValues" dxfId="393" priority="394"/>
-    <cfRule type="duplicateValues" dxfId="394" priority="395"/>
-    <cfRule type="duplicateValues" dxfId="395" priority="396"/>
-    <cfRule type="duplicateValues" dxfId="396" priority="397"/>
-    <cfRule type="duplicateValues" dxfId="397" priority="398"/>
-    <cfRule type="duplicateValues" dxfId="398" priority="399"/>
-    <cfRule type="duplicateValues" dxfId="399" priority="400"/>
-    <cfRule type="duplicateValues" dxfId="400" priority="401"/>
-    <cfRule type="duplicateValues" dxfId="401" priority="402"/>
-    <cfRule type="duplicateValues" dxfId="402" priority="403"/>
-    <cfRule type="duplicateValues" dxfId="403" priority="404"/>
-    <cfRule type="duplicateValues" dxfId="404" priority="405"/>
-    <cfRule type="duplicateValues" dxfId="405" priority="406"/>
-    <cfRule type="duplicateValues" dxfId="406" priority="407"/>
-    <cfRule type="duplicateValues" dxfId="407" priority="408"/>
-    <cfRule type="duplicateValues" dxfId="408" priority="409"/>
-    <cfRule type="duplicateValues" dxfId="409" priority="410"/>
-    <cfRule type="duplicateValues" dxfId="410" priority="411"/>
-    <cfRule type="duplicateValues" dxfId="411" priority="412"/>
-    <cfRule type="duplicateValues" dxfId="412" priority="413"/>
-    <cfRule type="duplicateValues" dxfId="413" priority="414"/>
-    <cfRule type="duplicateValues" dxfId="414" priority="415"/>
-    <cfRule type="duplicateValues" dxfId="415" priority="416"/>
-    <cfRule type="duplicateValues" dxfId="416" priority="417"/>
-    <cfRule type="duplicateValues" dxfId="417" priority="418"/>
-    <cfRule type="duplicateValues" dxfId="418" priority="419"/>
-    <cfRule type="duplicateValues" dxfId="419" priority="420"/>
-    <cfRule type="duplicateValues" dxfId="420" priority="421"/>
-    <cfRule type="duplicateValues" dxfId="421" priority="422"/>
-    <cfRule type="duplicateValues" dxfId="422" priority="423"/>
-    <cfRule type="duplicateValues" dxfId="423" priority="424"/>
-    <cfRule type="duplicateValues" dxfId="424" priority="425"/>
-    <cfRule type="duplicateValues" dxfId="425" priority="426"/>
-    <cfRule type="duplicateValues" dxfId="426" priority="427"/>
-    <cfRule type="duplicateValues" dxfId="427" priority="428"/>
-    <cfRule type="duplicateValues" dxfId="428" priority="429"/>
-    <cfRule type="duplicateValues" dxfId="429" priority="430"/>
-    <cfRule type="duplicateValues" dxfId="430" priority="431"/>
-    <cfRule type="duplicateValues" dxfId="431" priority="432"/>
-    <cfRule type="duplicateValues" dxfId="432" priority="433"/>
-    <cfRule type="duplicateValues" dxfId="433" priority="434"/>
-    <cfRule type="duplicateValues" dxfId="434" priority="435"/>
-    <cfRule type="duplicateValues" dxfId="435" priority="436"/>
-    <cfRule type="duplicateValues" dxfId="436" priority="437"/>
-    <cfRule type="duplicateValues" dxfId="437" priority="438"/>
-    <cfRule type="duplicateValues" dxfId="438" priority="439"/>
-    <cfRule type="duplicateValues" dxfId="439" priority="440"/>
-    <cfRule type="duplicateValues" dxfId="440" priority="441"/>
-    <cfRule type="duplicateValues" dxfId="441" priority="442"/>
-    <cfRule type="duplicateValues" dxfId="442" priority="443"/>
-    <cfRule type="duplicateValues" dxfId="443" priority="444"/>
-    <cfRule type="duplicateValues" dxfId="444" priority="445"/>
-    <cfRule type="duplicateValues" dxfId="445" priority="446"/>
-    <cfRule type="duplicateValues" dxfId="446" priority="447"/>
-    <cfRule type="duplicateValues" dxfId="447" priority="448"/>
-    <cfRule type="duplicateValues" dxfId="448" priority="449"/>
-    <cfRule type="duplicateValues" dxfId="449" priority="450"/>
-    <cfRule type="duplicateValues" dxfId="450" priority="451"/>
-    <cfRule type="duplicateValues" dxfId="451" priority="452"/>
-    <cfRule type="duplicateValues" dxfId="452" priority="453"/>
-    <cfRule type="duplicateValues" dxfId="453" priority="454"/>
-    <cfRule type="duplicateValues" dxfId="454" priority="455"/>
-    <cfRule type="duplicateValues" dxfId="455" priority="456"/>
-    <cfRule type="duplicateValues" dxfId="456" priority="457"/>
-    <cfRule type="duplicateValues" dxfId="457" priority="458"/>
-    <cfRule type="duplicateValues" dxfId="458" priority="459"/>
-    <cfRule type="duplicateValues" dxfId="459" priority="460"/>
-    <cfRule type="duplicateValues" dxfId="460" priority="461"/>
-    <cfRule type="duplicateValues" dxfId="461" priority="462"/>
-    <cfRule type="duplicateValues" dxfId="462" priority="463"/>
-    <cfRule type="duplicateValues" dxfId="463" priority="464"/>
-    <cfRule type="duplicateValues" dxfId="464" priority="465"/>
-    <cfRule type="duplicateValues" dxfId="465" priority="466"/>
-    <cfRule type="duplicateValues" dxfId="466" priority="467"/>
-    <cfRule type="duplicateValues" dxfId="467" priority="468"/>
-    <cfRule type="duplicateValues" dxfId="468" priority="469"/>
-    <cfRule type="duplicateValues" dxfId="469" priority="470"/>
-    <cfRule type="duplicateValues" dxfId="470" priority="471"/>
-    <cfRule type="duplicateValues" dxfId="471" priority="472"/>
-    <cfRule type="duplicateValues" dxfId="472" priority="473"/>
-    <cfRule type="duplicateValues" dxfId="473" priority="474"/>
-    <cfRule type="duplicateValues" dxfId="474" priority="475"/>
-    <cfRule type="duplicateValues" dxfId="475" priority="476"/>
-    <cfRule type="duplicateValues" dxfId="476" priority="477"/>
-    <cfRule type="duplicateValues" dxfId="477" priority="478"/>
-    <cfRule type="duplicateValues" dxfId="478" priority="479"/>
+    <cfRule type="duplicateValues" dxfId="511" priority="512"/>
+    <cfRule type="duplicateValues" dxfId="510" priority="511"/>
+    <cfRule type="duplicateValues" dxfId="509" priority="510"/>
+    <cfRule type="duplicateValues" dxfId="508" priority="509"/>
+    <cfRule type="duplicateValues" dxfId="507" priority="508"/>
+    <cfRule type="duplicateValues" dxfId="506" priority="507"/>
+    <cfRule type="duplicateValues" dxfId="505" priority="506"/>
+    <cfRule type="duplicateValues" dxfId="504" priority="505"/>
+    <cfRule type="duplicateValues" dxfId="503" priority="504"/>
+    <cfRule type="duplicateValues" dxfId="502" priority="503"/>
+    <cfRule type="duplicateValues" dxfId="501" priority="502"/>
+    <cfRule type="duplicateValues" dxfId="500" priority="501"/>
+    <cfRule type="duplicateValues" dxfId="499" priority="500"/>
+    <cfRule type="duplicateValues" dxfId="498" priority="499"/>
+    <cfRule type="duplicateValues" dxfId="497" priority="498"/>
+    <cfRule type="duplicateValues" dxfId="496" priority="497"/>
+    <cfRule type="duplicateValues" dxfId="495" priority="496"/>
+    <cfRule type="duplicateValues" dxfId="494" priority="495"/>
+    <cfRule type="duplicateValues" dxfId="493" priority="494"/>
+    <cfRule type="duplicateValues" dxfId="492" priority="493"/>
+    <cfRule type="duplicateValues" dxfId="491" priority="492"/>
+    <cfRule type="duplicateValues" dxfId="490" priority="491"/>
+    <cfRule type="duplicateValues" dxfId="489" priority="490"/>
+    <cfRule type="duplicateValues" dxfId="488" priority="489"/>
+    <cfRule type="duplicateValues" dxfId="487" priority="488"/>
+    <cfRule type="duplicateValues" dxfId="486" priority="487"/>
+    <cfRule type="duplicateValues" dxfId="485" priority="486"/>
+    <cfRule type="duplicateValues" dxfId="484" priority="485"/>
+    <cfRule type="duplicateValues" dxfId="483" priority="484"/>
+    <cfRule type="duplicateValues" dxfId="482" priority="483"/>
+    <cfRule type="duplicateValues" dxfId="481" priority="482"/>
     <cfRule type="duplicateValues" dxfId="480" priority="480"/>
     <cfRule type="duplicateValues" dxfId="479" priority="481"/>
-    <cfRule type="duplicateValues" dxfId="481" priority="482"/>
-    <cfRule type="duplicateValues" dxfId="482" priority="483"/>
-    <cfRule type="duplicateValues" dxfId="483" priority="484"/>
-    <cfRule type="duplicateValues" dxfId="484" priority="485"/>
-    <cfRule type="duplicateValues" dxfId="485" priority="486"/>
-    <cfRule type="duplicateValues" dxfId="486" priority="487"/>
-    <cfRule type="duplicateValues" dxfId="487" priority="488"/>
-    <cfRule type="duplicateValues" dxfId="488" priority="489"/>
-    <cfRule type="duplicateValues" dxfId="489" priority="490"/>
-    <cfRule type="duplicateValues" dxfId="490" priority="491"/>
-    <cfRule type="duplicateValues" dxfId="491" priority="492"/>
-    <cfRule type="duplicateValues" dxfId="492" priority="493"/>
-    <cfRule type="duplicateValues" dxfId="493" priority="494"/>
-    <cfRule type="duplicateValues" dxfId="494" priority="495"/>
-    <cfRule type="duplicateValues" dxfId="495" priority="496"/>
-    <cfRule type="duplicateValues" dxfId="496" priority="497"/>
-    <cfRule type="duplicateValues" dxfId="497" priority="498"/>
-    <cfRule type="duplicateValues" dxfId="498" priority="499"/>
-    <cfRule type="duplicateValues" dxfId="499" priority="500"/>
-    <cfRule type="duplicateValues" dxfId="500" priority="501"/>
-    <cfRule type="duplicateValues" dxfId="501" priority="502"/>
-    <cfRule type="duplicateValues" dxfId="502" priority="503"/>
-    <cfRule type="duplicateValues" dxfId="503" priority="504"/>
-    <cfRule type="duplicateValues" dxfId="504" priority="505"/>
-    <cfRule type="duplicateValues" dxfId="505" priority="506"/>
-    <cfRule type="duplicateValues" dxfId="506" priority="507"/>
-    <cfRule type="duplicateValues" dxfId="507" priority="508"/>
-    <cfRule type="duplicateValues" dxfId="508" priority="509"/>
-    <cfRule type="duplicateValues" dxfId="509" priority="510"/>
-    <cfRule type="duplicateValues" dxfId="510" priority="511"/>
-    <cfRule type="duplicateValues" dxfId="511" priority="512"/>
+    <cfRule type="duplicateValues" dxfId="478" priority="479"/>
+    <cfRule type="duplicateValues" dxfId="477" priority="478"/>
+    <cfRule type="duplicateValues" dxfId="476" priority="477"/>
+    <cfRule type="duplicateValues" dxfId="475" priority="476"/>
+    <cfRule type="duplicateValues" dxfId="474" priority="475"/>
+    <cfRule type="duplicateValues" dxfId="473" priority="474"/>
+    <cfRule type="duplicateValues" dxfId="472" priority="473"/>
+    <cfRule type="duplicateValues" dxfId="471" priority="472"/>
+    <cfRule type="duplicateValues" dxfId="470" priority="471"/>
+    <cfRule type="duplicateValues" dxfId="469" priority="470"/>
+    <cfRule type="duplicateValues" dxfId="468" priority="469"/>
+    <cfRule type="duplicateValues" dxfId="467" priority="468"/>
+    <cfRule type="duplicateValues" dxfId="466" priority="467"/>
+    <cfRule type="duplicateValues" dxfId="465" priority="466"/>
+    <cfRule type="duplicateValues" dxfId="464" priority="465"/>
+    <cfRule type="duplicateValues" dxfId="463" priority="464"/>
+    <cfRule type="duplicateValues" dxfId="462" priority="463"/>
+    <cfRule type="duplicateValues" dxfId="461" priority="462"/>
+    <cfRule type="duplicateValues" dxfId="460" priority="461"/>
+    <cfRule type="duplicateValues" dxfId="459" priority="460"/>
+    <cfRule type="duplicateValues" dxfId="458" priority="459"/>
+    <cfRule type="duplicateValues" dxfId="457" priority="458"/>
+    <cfRule type="duplicateValues" dxfId="456" priority="457"/>
+    <cfRule type="duplicateValues" dxfId="455" priority="456"/>
+    <cfRule type="duplicateValues" dxfId="454" priority="455"/>
+    <cfRule type="duplicateValues" dxfId="453" priority="454"/>
+    <cfRule type="duplicateValues" dxfId="452" priority="453"/>
+    <cfRule type="duplicateValues" dxfId="451" priority="452"/>
+    <cfRule type="duplicateValues" dxfId="450" priority="451"/>
+    <cfRule type="duplicateValues" dxfId="449" priority="450"/>
+    <cfRule type="duplicateValues" dxfId="448" priority="449"/>
+    <cfRule type="duplicateValues" dxfId="447" priority="448"/>
+    <cfRule type="duplicateValues" dxfId="446" priority="447"/>
+    <cfRule type="duplicateValues" dxfId="445" priority="446"/>
+    <cfRule type="duplicateValues" dxfId="444" priority="445"/>
+    <cfRule type="duplicateValues" dxfId="443" priority="444"/>
+    <cfRule type="duplicateValues" dxfId="442" priority="443"/>
+    <cfRule type="duplicateValues" dxfId="441" priority="442"/>
+    <cfRule type="duplicateValues" dxfId="440" priority="441"/>
+    <cfRule type="duplicateValues" dxfId="439" priority="440"/>
+    <cfRule type="duplicateValues" dxfId="438" priority="439"/>
+    <cfRule type="duplicateValues" dxfId="437" priority="438"/>
+    <cfRule type="duplicateValues" dxfId="436" priority="437"/>
+    <cfRule type="duplicateValues" dxfId="435" priority="436"/>
+    <cfRule type="duplicateValues" dxfId="434" priority="435"/>
+    <cfRule type="duplicateValues" dxfId="433" priority="434"/>
+    <cfRule type="duplicateValues" dxfId="432" priority="433"/>
+    <cfRule type="duplicateValues" dxfId="431" priority="432"/>
+    <cfRule type="duplicateValues" dxfId="430" priority="431"/>
+    <cfRule type="duplicateValues" dxfId="429" priority="430"/>
+    <cfRule type="duplicateValues" dxfId="428" priority="429"/>
+    <cfRule type="duplicateValues" dxfId="427" priority="428"/>
+    <cfRule type="duplicateValues" dxfId="426" priority="427"/>
+    <cfRule type="duplicateValues" dxfId="425" priority="426"/>
+    <cfRule type="duplicateValues" dxfId="424" priority="425"/>
+    <cfRule type="duplicateValues" dxfId="423" priority="424"/>
+    <cfRule type="duplicateValues" dxfId="422" priority="423"/>
+    <cfRule type="duplicateValues" dxfId="421" priority="422"/>
+    <cfRule type="duplicateValues" dxfId="420" priority="421"/>
+    <cfRule type="duplicateValues" dxfId="419" priority="420"/>
+    <cfRule type="duplicateValues" dxfId="418" priority="419"/>
+    <cfRule type="duplicateValues" dxfId="417" priority="418"/>
+    <cfRule type="duplicateValues" dxfId="416" priority="417"/>
+    <cfRule type="duplicateValues" dxfId="415" priority="416"/>
+    <cfRule type="duplicateValues" dxfId="414" priority="415"/>
+    <cfRule type="duplicateValues" dxfId="413" priority="414"/>
+    <cfRule type="duplicateValues" dxfId="412" priority="413"/>
+    <cfRule type="duplicateValues" dxfId="411" priority="412"/>
+    <cfRule type="duplicateValues" dxfId="410" priority="411"/>
+    <cfRule type="duplicateValues" dxfId="409" priority="410"/>
+    <cfRule type="duplicateValues" dxfId="408" priority="409"/>
+    <cfRule type="duplicateValues" dxfId="407" priority="408"/>
+    <cfRule type="duplicateValues" dxfId="406" priority="407"/>
+    <cfRule type="duplicateValues" dxfId="405" priority="406"/>
+    <cfRule type="duplicateValues" dxfId="404" priority="405"/>
+    <cfRule type="duplicateValues" dxfId="403" priority="404"/>
+    <cfRule type="duplicateValues" dxfId="402" priority="403"/>
+    <cfRule type="duplicateValues" dxfId="401" priority="402"/>
+    <cfRule type="duplicateValues" dxfId="400" priority="401"/>
+    <cfRule type="duplicateValues" dxfId="399" priority="400"/>
+    <cfRule type="duplicateValues" dxfId="398" priority="399"/>
+    <cfRule type="duplicateValues" dxfId="397" priority="398"/>
+    <cfRule type="duplicateValues" dxfId="396" priority="397"/>
+    <cfRule type="duplicateValues" dxfId="395" priority="396"/>
+    <cfRule type="duplicateValues" dxfId="394" priority="395"/>
+    <cfRule type="duplicateValues" dxfId="393" priority="394"/>
+    <cfRule type="duplicateValues" dxfId="392" priority="393"/>
+    <cfRule type="duplicateValues" dxfId="391" priority="392"/>
+    <cfRule type="duplicateValues" dxfId="390" priority="391"/>
+    <cfRule type="duplicateValues" dxfId="389" priority="390"/>
+    <cfRule type="duplicateValues" dxfId="388" priority="389"/>
+    <cfRule type="duplicateValues" dxfId="387" priority="388"/>
+    <cfRule type="duplicateValues" dxfId="386" priority="387"/>
+    <cfRule type="duplicateValues" dxfId="385" priority="386"/>
+    <cfRule type="duplicateValues" dxfId="384" priority="385"/>
+    <cfRule type="duplicateValues" dxfId="383" priority="384"/>
+    <cfRule type="duplicateValues" dxfId="382" priority="383"/>
+    <cfRule type="duplicateValues" dxfId="381" priority="382"/>
+    <cfRule type="duplicateValues" dxfId="380" priority="381"/>
+    <cfRule type="duplicateValues" dxfId="379" priority="380"/>
+    <cfRule type="duplicateValues" dxfId="378" priority="379"/>
+    <cfRule type="duplicateValues" dxfId="377" priority="378"/>
+    <cfRule type="duplicateValues" dxfId="376" priority="377"/>
+    <cfRule type="duplicateValues" dxfId="375" priority="376"/>
+    <cfRule type="duplicateValues" dxfId="374" priority="375"/>
+    <cfRule type="duplicateValues" dxfId="373" priority="374"/>
+    <cfRule type="duplicateValues" dxfId="372" priority="373"/>
+    <cfRule type="duplicateValues" dxfId="371" priority="372"/>
+    <cfRule type="duplicateValues" dxfId="370" priority="371"/>
+    <cfRule type="duplicateValues" dxfId="369" priority="370"/>
+    <cfRule type="duplicateValues" dxfId="368" priority="369"/>
+    <cfRule type="duplicateValues" dxfId="367" priority="368"/>
+    <cfRule type="duplicateValues" dxfId="366" priority="367"/>
+    <cfRule type="duplicateValues" dxfId="365" priority="366"/>
+    <cfRule type="duplicateValues" dxfId="364" priority="365"/>
+    <cfRule type="duplicateValues" dxfId="363" priority="364"/>
+    <cfRule type="duplicateValues" dxfId="362" priority="363"/>
+    <cfRule type="duplicateValues" dxfId="361" priority="362"/>
+    <cfRule type="duplicateValues" dxfId="360" priority="361"/>
+    <cfRule type="duplicateValues" dxfId="359" priority="360"/>
+    <cfRule type="duplicateValues" dxfId="358" priority="359"/>
+    <cfRule type="duplicateValues" dxfId="357" priority="358"/>
+    <cfRule type="duplicateValues" dxfId="356" priority="357"/>
+    <cfRule type="duplicateValues" dxfId="355" priority="356"/>
+    <cfRule type="duplicateValues" dxfId="354" priority="355"/>
+    <cfRule type="duplicateValues" dxfId="353" priority="354"/>
+    <cfRule type="duplicateValues" dxfId="352" priority="353"/>
+    <cfRule type="duplicateValues" dxfId="351" priority="352"/>
+    <cfRule type="duplicateValues" dxfId="350" priority="351"/>
+    <cfRule type="duplicateValues" dxfId="349" priority="350"/>
+    <cfRule type="duplicateValues" dxfId="348" priority="349"/>
+    <cfRule type="duplicateValues" dxfId="347" priority="348"/>
+    <cfRule type="duplicateValues" dxfId="346" priority="347"/>
+    <cfRule type="duplicateValues" dxfId="345" priority="346"/>
+    <cfRule type="duplicateValues" dxfId="344" priority="345"/>
+    <cfRule type="duplicateValues" dxfId="343" priority="344"/>
+    <cfRule type="duplicateValues" dxfId="342" priority="343"/>
+    <cfRule type="duplicateValues" dxfId="341" priority="342"/>
+    <cfRule type="duplicateValues" dxfId="340" priority="341"/>
+    <cfRule type="duplicateValues" dxfId="339" priority="340"/>
+    <cfRule type="duplicateValues" dxfId="338" priority="339"/>
+    <cfRule type="duplicateValues" dxfId="337" priority="338"/>
+    <cfRule type="duplicateValues" dxfId="336" priority="337"/>
+    <cfRule type="duplicateValues" dxfId="335" priority="336"/>
+    <cfRule type="duplicateValues" dxfId="334" priority="335"/>
+    <cfRule type="duplicateValues" dxfId="333" priority="334"/>
+    <cfRule type="duplicateValues" dxfId="332" priority="333"/>
+    <cfRule type="duplicateValues" dxfId="331" priority="332"/>
+    <cfRule type="duplicateValues" dxfId="330" priority="331"/>
+    <cfRule type="duplicateValues" dxfId="329" priority="330"/>
+    <cfRule type="duplicateValues" dxfId="328" priority="329"/>
+    <cfRule type="duplicateValues" dxfId="327" priority="328"/>
+    <cfRule type="duplicateValues" dxfId="326" priority="327"/>
+    <cfRule type="duplicateValues" dxfId="325" priority="326"/>
+    <cfRule type="duplicateValues" dxfId="324" priority="325"/>
+    <cfRule type="duplicateValues" dxfId="323" priority="324"/>
+    <cfRule type="duplicateValues" dxfId="322" priority="323"/>
+    <cfRule type="duplicateValues" dxfId="321" priority="322"/>
+    <cfRule type="duplicateValues" dxfId="320" priority="321"/>
+    <cfRule type="duplicateValues" dxfId="319" priority="320"/>
+    <cfRule type="duplicateValues" dxfId="318" priority="319"/>
+    <cfRule type="duplicateValues" dxfId="317" priority="318"/>
+    <cfRule type="duplicateValues" dxfId="316" priority="317"/>
+    <cfRule type="duplicateValues" dxfId="315" priority="316"/>
+    <cfRule type="duplicateValues" dxfId="314" priority="315"/>
+    <cfRule type="duplicateValues" dxfId="313" priority="314"/>
+    <cfRule type="duplicateValues" dxfId="312" priority="313"/>
+    <cfRule type="duplicateValues" dxfId="311" priority="312"/>
+    <cfRule type="duplicateValues" dxfId="310" priority="311"/>
+    <cfRule type="duplicateValues" dxfId="309" priority="310"/>
+    <cfRule type="duplicateValues" dxfId="308" priority="309"/>
+    <cfRule type="duplicateValues" dxfId="307" priority="308"/>
+    <cfRule type="duplicateValues" dxfId="306" priority="307"/>
+    <cfRule type="duplicateValues" dxfId="305" priority="306"/>
+    <cfRule type="duplicateValues" dxfId="304" priority="305"/>
+    <cfRule type="duplicateValues" dxfId="303" priority="304"/>
+    <cfRule type="duplicateValues" dxfId="302" priority="303"/>
+    <cfRule type="duplicateValues" dxfId="301" priority="302"/>
+    <cfRule type="duplicateValues" dxfId="300" priority="301"/>
+    <cfRule type="duplicateValues" dxfId="299" priority="300"/>
+    <cfRule type="duplicateValues" dxfId="298" priority="299"/>
+    <cfRule type="duplicateValues" dxfId="297" priority="298"/>
+    <cfRule type="duplicateValues" dxfId="296" priority="297"/>
+    <cfRule type="duplicateValues" dxfId="295" priority="296"/>
+    <cfRule type="duplicateValues" dxfId="294" priority="295"/>
+    <cfRule type="duplicateValues" dxfId="293" priority="294"/>
+    <cfRule type="duplicateValues" dxfId="292" priority="293"/>
+    <cfRule type="duplicateValues" dxfId="291" priority="292"/>
+    <cfRule type="duplicateValues" dxfId="290" priority="291"/>
+    <cfRule type="duplicateValues" dxfId="289" priority="290"/>
+    <cfRule type="duplicateValues" dxfId="288" priority="289"/>
+    <cfRule type="duplicateValues" dxfId="287" priority="288"/>
+    <cfRule type="duplicateValues" dxfId="286" priority="287"/>
+    <cfRule type="duplicateValues" dxfId="285" priority="286"/>
+    <cfRule type="duplicateValues" dxfId="284" priority="285"/>
+    <cfRule type="duplicateValues" dxfId="283" priority="284"/>
+    <cfRule type="duplicateValues" dxfId="282" priority="283"/>
+    <cfRule type="duplicateValues" dxfId="281" priority="282"/>
+    <cfRule type="duplicateValues" dxfId="280" priority="281"/>
+    <cfRule type="duplicateValues" dxfId="279" priority="280"/>
+    <cfRule type="duplicateValues" dxfId="278" priority="279"/>
+    <cfRule type="duplicateValues" dxfId="277" priority="278"/>
+    <cfRule type="duplicateValues" dxfId="276" priority="277"/>
+    <cfRule type="duplicateValues" dxfId="275" priority="276"/>
+    <cfRule type="duplicateValues" dxfId="274" priority="275"/>
+    <cfRule type="duplicateValues" dxfId="273" priority="274"/>
+    <cfRule type="duplicateValues" dxfId="272" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="271" priority="272"/>
+    <cfRule type="duplicateValues" dxfId="270" priority="271"/>
+    <cfRule type="duplicateValues" dxfId="269" priority="270"/>
+    <cfRule type="duplicateValues" dxfId="268" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="267" priority="268"/>
+    <cfRule type="duplicateValues" dxfId="266" priority="267"/>
+    <cfRule type="duplicateValues" dxfId="265" priority="266"/>
+    <cfRule type="duplicateValues" dxfId="264" priority="265"/>
+    <cfRule type="duplicateValues" dxfId="263" priority="264"/>
+    <cfRule type="duplicateValues" dxfId="262" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="262"/>
+    <cfRule type="duplicateValues" dxfId="260" priority="261"/>
+    <cfRule type="duplicateValues" dxfId="259" priority="260"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="259"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="258"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="257"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="256"/>
+    <cfRule type="duplicateValues" dxfId="254" priority="255"/>
+    <cfRule type="duplicateValues" dxfId="253" priority="254"/>
+    <cfRule type="duplicateValues" dxfId="252" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="251" priority="252"/>
+    <cfRule type="duplicateValues" dxfId="250" priority="251"/>
+    <cfRule type="duplicateValues" dxfId="249" priority="250"/>
+    <cfRule type="duplicateValues" dxfId="248" priority="249"/>
+    <cfRule type="duplicateValues" dxfId="247" priority="248"/>
+    <cfRule type="duplicateValues" dxfId="246" priority="247"/>
+    <cfRule type="duplicateValues" dxfId="245" priority="246"/>
+    <cfRule type="duplicateValues" dxfId="244" priority="245"/>
+    <cfRule type="duplicateValues" dxfId="243" priority="244"/>
+    <cfRule type="duplicateValues" dxfId="242" priority="243"/>
+    <cfRule type="duplicateValues" dxfId="241" priority="242"/>
+    <cfRule type="duplicateValues" dxfId="240" priority="241"/>
+    <cfRule type="duplicateValues" dxfId="239" priority="240"/>
+    <cfRule type="duplicateValues" dxfId="238" priority="239"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="236" priority="237"/>
+    <cfRule type="duplicateValues" dxfId="235" priority="236"/>
+    <cfRule type="duplicateValues" dxfId="234" priority="235"/>
+    <cfRule type="duplicateValues" dxfId="233" priority="234"/>
+    <cfRule type="duplicateValues" dxfId="232" priority="233"/>
+    <cfRule type="duplicateValues" dxfId="231" priority="232"/>
+    <cfRule type="duplicateValues" dxfId="230" priority="231"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="230"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="229"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="228"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="227"/>
+    <cfRule type="duplicateValues" dxfId="225" priority="226"/>
+    <cfRule type="duplicateValues" dxfId="224" priority="225"/>
+    <cfRule type="duplicateValues" dxfId="223" priority="224"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="223"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="222"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="221"/>
+    <cfRule type="duplicateValues" dxfId="219" priority="220"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="219"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="217"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="216"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="215"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="214"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="212"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="211"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="210"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="209"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="207"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="206"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="203"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="202"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="166"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
